--- a/data/seed/2026-09/export_20260930_0621.xlsx
+++ b/data/seed/2026-09/export_20260930_0621.xlsx
@@ -38,628 +38,628 @@
     <t>Branch</t>
   </si>
   <si>
-    <t>AIBL-2026-510211</t>
+    <t>AIBL-2026-364527</t>
   </si>
   <si>
     <t>New Business</t>
   </si>
   <si>
+    <t>Policy Issuance - Single Premium</t>
+  </si>
+  <si>
+    <t>Completed - STP</t>
+  </si>
+  <si>
+    <t>Dublin</t>
+  </si>
+  <si>
+    <t>AIBL-2026-570424</t>
+  </si>
+  <si>
+    <t>Underwriting</t>
+  </si>
+  <si>
+    <t>Standard UW Decision</t>
+  </si>
+  <si>
+    <t>Cork</t>
+  </si>
+  <si>
+    <t>AIBL-2026-517341</t>
+  </si>
+  <si>
+    <t>Medical UW</t>
+  </si>
+  <si>
+    <t>AIBL-2026-824098</t>
+  </si>
+  <si>
+    <t>Endorsement</t>
+  </si>
+  <si>
+    <t>Beneficiary Change</t>
+  </si>
+  <si>
+    <t>AIBL-2026-404049</t>
+  </si>
+  <si>
+    <t>Waterford</t>
+  </si>
+  <si>
+    <t>AIBL-2026-773320</t>
+  </si>
+  <si>
+    <t>Policy Issuance - Regular Premium</t>
+  </si>
+  <si>
+    <t>Galway</t>
+  </si>
+  <si>
+    <t>AIBL-2026-909537</t>
+  </si>
+  <si>
+    <t>Completed - Manual</t>
+  </si>
+  <si>
+    <t>AIBL-2026-957295</t>
+  </si>
+  <si>
+    <t>Claim</t>
+  </si>
+  <si>
+    <t>Death Claim</t>
+  </si>
+  <si>
+    <t>Limerick</t>
+  </si>
+  <si>
+    <t>AIBL-2026-585008</t>
+  </si>
+  <si>
+    <t>Sum Assured Alteration</t>
+  </si>
+  <si>
+    <t>AIBL-2026-393774</t>
+  </si>
+  <si>
+    <t>Address Change</t>
+  </si>
+  <si>
+    <t>AIBL-2026-317838</t>
+  </si>
+  <si>
+    <t>AIBL-2026-679233</t>
+  </si>
+  <si>
+    <t>AIBL-2026-571833</t>
+  </si>
+  <si>
+    <t>AIBL-2026-442504</t>
+  </si>
+  <si>
+    <t>AIBL-2026-439712</t>
+  </si>
+  <si>
+    <t>AIBL-2026-986110</t>
+  </si>
+  <si>
+    <t>AIBL-2026-649711</t>
+  </si>
+  <si>
+    <t>AIBL-2026-920653</t>
+  </si>
+  <si>
+    <t>AIBL-2026-885790</t>
+  </si>
+  <si>
+    <t>AIBL-2026-174791</t>
+  </si>
+  <si>
+    <t>AIBL-2026-531155</t>
+  </si>
+  <si>
+    <t>Premium Frequency Change</t>
+  </si>
+  <si>
+    <t>AIBL-2026-770128</t>
+  </si>
+  <si>
     <t>Policy Issuance</t>
   </si>
   <si>
-    <t>Completed - STP</t>
-  </si>
-  <si>
-    <t>Waterford</t>
-  </si>
-  <si>
-    <t>AIBL-2026-629354</t>
-  </si>
-  <si>
-    <t>Underwriting</t>
-  </si>
-  <si>
-    <t>Medical UW</t>
-  </si>
-  <si>
-    <t>Dublin</t>
-  </si>
-  <si>
-    <t>AIBL-2026-639558</t>
-  </si>
-  <si>
-    <t>Claim</t>
+    <t>AIBL-2026-832565</t>
+  </si>
+  <si>
+    <t>AIBL-2026-730739</t>
+  </si>
+  <si>
+    <t>AIBL-2026-838005</t>
+  </si>
+  <si>
+    <t>AIBL-2026-251072</t>
+  </si>
+  <si>
+    <t>AIBL-2026-810614</t>
+  </si>
+  <si>
+    <t>AIBL-2026-228698</t>
+  </si>
+  <si>
+    <t>AIBL-2026-541458</t>
+  </si>
+  <si>
+    <t>Financial UW</t>
+  </si>
+  <si>
+    <t>AIBL-2026-722896</t>
+  </si>
+  <si>
+    <t>AIBL-2026-923419</t>
+  </si>
+  <si>
+    <t>AIBL-2026-334078</t>
+  </si>
+  <si>
+    <t>AIBL-2026-990152</t>
   </si>
   <si>
     <t>Maturity Claim</t>
   </si>
   <si>
-    <t>Limerick</t>
-  </si>
-  <si>
-    <t>AIBL-2026-507572</t>
+    <t>AIBL-2026-751494</t>
+  </si>
+  <si>
+    <t>AIBL-2026-155300</t>
+  </si>
+  <si>
+    <t>AIBL-2026-417551</t>
+  </si>
+  <si>
+    <t>AIBL-2026-338319</t>
+  </si>
+  <si>
+    <t>AIBL-2026-499159</t>
+  </si>
+  <si>
+    <t>AIBL-2026-230433</t>
+  </si>
+  <si>
+    <t>AIBL-2026-458596</t>
+  </si>
+  <si>
+    <t>AIBL-2026-219245</t>
+  </si>
+  <si>
+    <t>AIBL-2026-219965</t>
+  </si>
+  <si>
+    <t>Income Protection Claim</t>
+  </si>
+  <si>
+    <t>AIBL-2026-192725</t>
+  </si>
+  <si>
+    <t>AIBL-2026-868213</t>
+  </si>
+  <si>
+    <t>AIBL-2026-216481</t>
+  </si>
+  <si>
+    <t>AIBL-2026-933769</t>
+  </si>
+  <si>
+    <t>AIBL-2026-743602</t>
+  </si>
+  <si>
+    <t>AIBL-2026-882147</t>
+  </si>
+  <si>
+    <t>AIBL-2026-919380</t>
+  </si>
+  <si>
+    <t>AIBL-2026-109236</t>
+  </si>
+  <si>
+    <t>AIBL-2026-507368</t>
+  </si>
+  <si>
+    <t>AIBL-2026-568237</t>
+  </si>
+  <si>
+    <t>AIBL-2026-110027</t>
+  </si>
+  <si>
+    <t>AIBL-2026-256633</t>
+  </si>
+  <si>
+    <t>AIBL-2026-590791</t>
+  </si>
+  <si>
+    <t>AIBL-2026-190963</t>
+  </si>
+  <si>
+    <t>AIBL-2026-623094</t>
+  </si>
+  <si>
+    <t>AIBL-2026-409275</t>
+  </si>
+  <si>
+    <t>AIBL-2026-137308</t>
+  </si>
+  <si>
+    <t>AIBL-2026-835408</t>
+  </si>
+  <si>
+    <t>AIBL-2026-125133</t>
+  </si>
+  <si>
+    <t>AIBL-2026-611763</t>
+  </si>
+  <si>
+    <t>AIBL-2026-280996</t>
+  </si>
+  <si>
+    <t>AIBL-2026-130466</t>
+  </si>
+  <si>
+    <t>AIBL-2026-764575</t>
+  </si>
+  <si>
+    <t>AIBL-2026-345840</t>
+  </si>
+  <si>
+    <t>AIBL-2026-451446</t>
+  </si>
+  <si>
+    <t>AIBL-2026-892982</t>
+  </si>
+  <si>
+    <t>AIBL-2026-315626</t>
+  </si>
+  <si>
+    <t>AIBL-2026-482544</t>
+  </si>
+  <si>
+    <t>AIBL-2026-327573</t>
+  </si>
+  <si>
+    <t>AIBL-2026-479634</t>
+  </si>
+  <si>
+    <t>AIBL-2026-506644</t>
+  </si>
+  <si>
+    <t>AIBL-2026-848808</t>
+  </si>
+  <si>
+    <t>AIBL-2026-194357</t>
+  </si>
+  <si>
+    <t>AIBL-2026-906838</t>
+  </si>
+  <si>
+    <t>AIBL-2026-141055</t>
+  </si>
+  <si>
+    <t>AIBL-2026-382840</t>
   </si>
   <si>
     <t>Critical Illness Claim</t>
   </si>
   <si>
-    <t>AIBL-2026-132164</t>
-  </si>
-  <si>
-    <t>Endorsement</t>
-  </si>
-  <si>
-    <t>Beneficiary Change</t>
-  </si>
-  <si>
-    <t>AIBL-2026-734970</t>
-  </si>
-  <si>
-    <t>Premium Frequency Change</t>
-  </si>
-  <si>
-    <t>Galway</t>
-  </si>
-  <si>
-    <t>AIBL-2026-558614</t>
-  </si>
-  <si>
-    <t>Policy Issuance - Regular Premium</t>
-  </si>
-  <si>
-    <t>Cork</t>
-  </si>
-  <si>
-    <t>AIBL-2026-764289</t>
-  </si>
-  <si>
-    <t>Policy Issuance - Single Premium</t>
-  </si>
-  <si>
-    <t>AIBL-2026-773320</t>
-  </si>
-  <si>
-    <t>Completed - Manual</t>
-  </si>
-  <si>
-    <t>AIBL-2026-906392</t>
+    <t>AIBL-2026-736124</t>
+  </si>
+  <si>
+    <t>AIBL-2026-703526</t>
+  </si>
+  <si>
+    <t>AIBL-2026-556801</t>
+  </si>
+  <si>
+    <t>AIBL-2026-610685</t>
+  </si>
+  <si>
+    <t>AIBL-2026-537891</t>
+  </si>
+  <si>
+    <t>AIBL-2026-733045</t>
+  </si>
+  <si>
+    <t>AIBL-2026-697746</t>
+  </si>
+  <si>
+    <t>AIBL-2026-650140</t>
+  </si>
+  <si>
+    <t>AIBL-2026-532582</t>
+  </si>
+  <si>
+    <t>AIBL-2026-366786</t>
+  </si>
+  <si>
+    <t>AIBL-2026-344424</t>
+  </si>
+  <si>
+    <t>AIBL-2026-961993</t>
+  </si>
+  <si>
+    <t>AIBL-2026-881691</t>
+  </si>
+  <si>
+    <t>AIBL-2026-359206</t>
+  </si>
+  <si>
+    <t>AIBL-2026-201958</t>
+  </si>
+  <si>
+    <t>AIBL-2026-868560</t>
+  </si>
+  <si>
+    <t>AIBL-2026-879346</t>
+  </si>
+  <si>
+    <t>AIBL-2026-262553</t>
+  </si>
+  <si>
+    <t>AIBL-2026-432606</t>
+  </si>
+  <si>
+    <t>AIBL-2026-943400</t>
+  </si>
+  <si>
+    <t>AIBL-2026-452467</t>
+  </si>
+  <si>
+    <t>AIBL-2026-378863</t>
+  </si>
+  <si>
+    <t>AIBL-2026-830472</t>
+  </si>
+  <si>
+    <t>AIBL-2026-575070</t>
+  </si>
+  <si>
+    <t>AIBL-2026-358512</t>
+  </si>
+  <si>
+    <t>AIBL-2026-172270</t>
+  </si>
+  <si>
+    <t>AIBL-2026-371807</t>
+  </si>
+  <si>
+    <t>AIBL-2026-556993</t>
+  </si>
+  <si>
+    <t>AIBL-2026-660341</t>
+  </si>
+  <si>
+    <t>AIBL-2026-461637</t>
+  </si>
+  <si>
+    <t>AIBL-2026-554502</t>
+  </si>
+  <si>
+    <t>AIBL-2026-947794</t>
+  </si>
+  <si>
+    <t>AIBL-2026-599290</t>
+  </si>
+  <si>
+    <t>AIBL-2026-260333</t>
+  </si>
+  <si>
+    <t>AIBL-2026-404298</t>
+  </si>
+  <si>
+    <t>AIBL-2026-832177</t>
+  </si>
+  <si>
+    <t>AIBL-2026-217925</t>
+  </si>
+  <si>
+    <t>AIBL-2026-414913</t>
+  </si>
+  <si>
+    <t>AIBL-2026-616263</t>
+  </si>
+  <si>
+    <t>AIBL-2026-690630</t>
+  </si>
+  <si>
+    <t>AIBL-2026-584782</t>
+  </si>
+  <si>
+    <t>AIBL-2026-307963</t>
+  </si>
+  <si>
+    <t>AIBL-2026-739320</t>
+  </si>
+  <si>
+    <t>AIBL-2026-887715</t>
+  </si>
+  <si>
+    <t>AIBL-2026-922069</t>
+  </si>
+  <si>
+    <t>AIBL-2026-515520</t>
+  </si>
+  <si>
+    <t>AIBL-2026-716360</t>
+  </si>
+  <si>
+    <t>AIBL-2026-203127</t>
+  </si>
+  <si>
+    <t>AIBL-2026-539310</t>
+  </si>
+  <si>
+    <t>AIBL-2026-853700</t>
+  </si>
+  <si>
+    <t>AIBL-2026-562102</t>
+  </si>
+  <si>
+    <t>AIBL-2026-108790</t>
+  </si>
+  <si>
+    <t>AIBL-2026-959170</t>
+  </si>
+  <si>
+    <t>AIBL-2026-324929</t>
+  </si>
+  <si>
+    <t>AIBL-2026-176623</t>
+  </si>
+  <si>
+    <t>AIBL-2026-453018</t>
+  </si>
+  <si>
+    <t>AIBL-2026-477510</t>
+  </si>
+  <si>
+    <t>AIBL-2026-419728</t>
+  </si>
+  <si>
+    <t>AIBL-2026-962764</t>
+  </si>
+  <si>
+    <t>AIBL-2026-232562</t>
+  </si>
+  <si>
+    <t>AIBL-2026-469458</t>
+  </si>
+  <si>
+    <t>AIBL-2026-443297</t>
+  </si>
+  <si>
+    <t>AIBL-2026-387918</t>
+  </si>
+  <si>
+    <t>AIBL-2026-892507</t>
+  </si>
+  <si>
+    <t>AIBL-2026-928918</t>
+  </si>
+  <si>
+    <t>AIBL-2026-295301</t>
+  </si>
+  <si>
+    <t>AIBL-2026-268024</t>
+  </si>
+  <si>
+    <t>AIBL-2026-401746</t>
+  </si>
+  <si>
+    <t>AIBL-2026-534518</t>
+  </si>
+  <si>
+    <t>AIBL-2026-151111</t>
+  </si>
+  <si>
+    <t>AIBL-2026-961153</t>
+  </si>
+  <si>
+    <t>AIBL-2026-929309</t>
+  </si>
+  <si>
+    <t>AIBL-2026-851773</t>
+  </si>
+  <si>
+    <t>AIBL-2026-700489</t>
+  </si>
+  <si>
+    <t>AIBL-2026-738032</t>
+  </si>
+  <si>
+    <t>AIBL-2026-381677</t>
+  </si>
+  <si>
+    <t>AIBL-2026-409200</t>
+  </si>
+  <si>
+    <t>AIBL-2026-438845</t>
+  </si>
+  <si>
+    <t>AIBL-2026-845889</t>
+  </si>
+  <si>
+    <t>AIBL-2026-245225</t>
+  </si>
+  <si>
+    <t>AIBL-2026-281311</t>
+  </si>
+  <si>
+    <t>AIBL-2026-192829</t>
+  </si>
+  <si>
+    <t>AIBL-2026-409608</t>
+  </si>
+  <si>
+    <t>AIBL-2026-221458</t>
   </si>
   <si>
     <t>Completed - Rework Required</t>
   </si>
   <si>
-    <t>AIBL-2026-754989</t>
-  </si>
-  <si>
-    <t>Financial UW</t>
-  </si>
-  <si>
-    <t>AIBL-2026-393774</t>
-  </si>
-  <si>
-    <t>Address Change</t>
-  </si>
-  <si>
-    <t>AIBL-2026-679233</t>
-  </si>
-  <si>
-    <t>AIBL-2026-872954</t>
-  </si>
-  <si>
-    <t>AIBL-2026-297370</t>
-  </si>
-  <si>
-    <t>AIBL-2026-920653</t>
-  </si>
-  <si>
-    <t>AIBL-2026-711339</t>
-  </si>
-  <si>
-    <t>Income Protection Claim</t>
-  </si>
-  <si>
-    <t>AIBL-2026-569554</t>
-  </si>
-  <si>
-    <t>AIBL-2026-544067</t>
-  </si>
-  <si>
-    <t>AIBL-2026-920480</t>
-  </si>
-  <si>
-    <t>AIBL-2026-531155</t>
-  </si>
-  <si>
-    <t>AIBL-2026-302972</t>
-  </si>
-  <si>
-    <t>AIBL-2026-897136</t>
-  </si>
-  <si>
-    <t>AIBL-2026-315997</t>
-  </si>
-  <si>
-    <t>AIBL-2026-618365</t>
-  </si>
-  <si>
-    <t>Standard UW Decision</t>
-  </si>
-  <si>
-    <t>AIBL-2026-640533</t>
-  </si>
-  <si>
-    <t>AIBL-2026-112782</t>
-  </si>
-  <si>
-    <t>AIBL-2026-641209</t>
-  </si>
-  <si>
-    <t>AIBL-2026-928132</t>
-  </si>
-  <si>
-    <t>AIBL-2026-251072</t>
-  </si>
-  <si>
-    <t>AIBL-2026-982017</t>
-  </si>
-  <si>
-    <t>AIBL-2026-527325</t>
-  </si>
-  <si>
-    <t>AIBL-2026-264452</t>
-  </si>
-  <si>
-    <t>AIBL-2026-520230</t>
-  </si>
-  <si>
-    <t>AIBL-2026-228698</t>
-  </si>
-  <si>
-    <t>AIBL-2026-722896</t>
-  </si>
-  <si>
-    <t>AIBL-2026-437549</t>
-  </si>
-  <si>
-    <t>AIBL-2026-923419</t>
-  </si>
-  <si>
-    <t>AIBL-2026-154827</t>
-  </si>
-  <si>
-    <t>AIBL-2026-151185</t>
-  </si>
-  <si>
-    <t>AIBL-2026-990152</t>
-  </si>
-  <si>
-    <t>AIBL-2026-394188</t>
-  </si>
-  <si>
-    <t>AIBL-2026-769505</t>
-  </si>
-  <si>
-    <t>AIBL-2026-826749</t>
-  </si>
-  <si>
-    <t>AIBL-2026-200937</t>
-  </si>
-  <si>
-    <t>AIBL-2026-297857</t>
-  </si>
-  <si>
-    <t>AIBL-2026-823331</t>
-  </si>
-  <si>
-    <t>AIBL-2026-582096</t>
-  </si>
-  <si>
-    <t>AIBL-2026-523614</t>
-  </si>
-  <si>
-    <t>AIBL-2026-458596</t>
-  </si>
-  <si>
-    <t>AIBL-2026-684352</t>
-  </si>
-  <si>
-    <t>AIBL-2026-490771</t>
-  </si>
-  <si>
-    <t>AIBL-2026-255187</t>
-  </si>
-  <si>
-    <t>AIBL-2026-660892</t>
-  </si>
-  <si>
-    <t>AIBL-2026-949849</t>
-  </si>
-  <si>
-    <t>AIBL-2026-548698</t>
-  </si>
-  <si>
-    <t>AIBL-2026-933769</t>
-  </si>
-  <si>
-    <t>AIBL-2026-882147</t>
-  </si>
-  <si>
-    <t>AIBL-2026-259280</t>
-  </si>
-  <si>
-    <t>AIBL-2026-558059</t>
-  </si>
-  <si>
-    <t>AIBL-2026-507368</t>
-  </si>
-  <si>
-    <t>AIBL-2026-378330</t>
-  </si>
-  <si>
-    <t>AIBL-2026-875086</t>
-  </si>
-  <si>
-    <t>AIBL-2026-253663</t>
-  </si>
-  <si>
-    <t>AIBL-2026-568237</t>
-  </si>
-  <si>
-    <t>AIBL-2026-714124</t>
-  </si>
-  <si>
-    <t>Sum Assured Alteration</t>
-  </si>
-  <si>
-    <t>AIBL-2026-426978</t>
-  </si>
-  <si>
-    <t>AIBL-2026-847616</t>
-  </si>
-  <si>
-    <t>AIBL-2026-590791</t>
-  </si>
-  <si>
-    <t>AIBL-2026-973423</t>
-  </si>
-  <si>
-    <t>AIBL-2026-572514</t>
-  </si>
-  <si>
-    <t>AIBL-2026-409275</t>
-  </si>
-  <si>
-    <t>AIBL-2026-145528</t>
-  </si>
-  <si>
-    <t>AIBL-2026-752850</t>
-  </si>
-  <si>
-    <t>AIBL-2026-105725</t>
-  </si>
-  <si>
-    <t>AIBL-2026-623016</t>
-  </si>
-  <si>
-    <t>AIBL-2026-592210</t>
-  </si>
-  <si>
-    <t>AIBL-2026-611763</t>
-  </si>
-  <si>
-    <t>AIBL-2026-451446</t>
-  </si>
-  <si>
-    <t>AIBL-2026-824087</t>
-  </si>
-  <si>
-    <t>AIBL-2026-709968</t>
-  </si>
-  <si>
-    <t>AIBL-2026-325250</t>
-  </si>
-  <si>
-    <t>AIBL-2026-116149</t>
-  </si>
-  <si>
-    <t>AIBL-2026-136657</t>
-  </si>
-  <si>
-    <t>AIBL-2026-257131</t>
-  </si>
-  <si>
-    <t>AIBL-2026-660774</t>
-  </si>
-  <si>
-    <t>AIBL-2026-141055</t>
-  </si>
-  <si>
-    <t>AIBL-2026-280842</t>
-  </si>
-  <si>
-    <t>AIBL-2026-844203</t>
-  </si>
-  <si>
-    <t>AIBL-2026-703526</t>
-  </si>
-  <si>
-    <t>AIBL-2026-537891</t>
-  </si>
-  <si>
-    <t>AIBL-2026-155441</t>
-  </si>
-  <si>
-    <t>AIBL-2026-636753</t>
-  </si>
-  <si>
-    <t>AIBL-2026-208201</t>
-  </si>
-  <si>
-    <t>AIBL-2026-671073</t>
-  </si>
-  <si>
-    <t>AIBL-2026-713108</t>
-  </si>
-  <si>
-    <t>Death Claim</t>
-  </si>
-  <si>
-    <t>AIBL-2026-961993</t>
-  </si>
-  <si>
-    <t>AIBL-2026-881691</t>
-  </si>
-  <si>
-    <t>AIBL-2026-295203</t>
-  </si>
-  <si>
-    <t>AIBL-2026-356000</t>
-  </si>
-  <si>
-    <t>AIBL-2026-201958</t>
-  </si>
-  <si>
-    <t>AIBL-2026-773221</t>
-  </si>
-  <si>
-    <t>AIBL-2026-539535</t>
-  </si>
-  <si>
-    <t>AIBL-2026-487105</t>
-  </si>
-  <si>
-    <t>AIBL-2026-262553</t>
-  </si>
-  <si>
-    <t>AIBL-2026-484356</t>
-  </si>
-  <si>
-    <t>AIBL-2026-426374</t>
-  </si>
-  <si>
-    <t>AIBL-2026-972765</t>
-  </si>
-  <si>
-    <t>AIBL-2026-267635</t>
-  </si>
-  <si>
-    <t>AIBL-2026-467760</t>
-  </si>
-  <si>
-    <t>AIBL-2026-281580</t>
-  </si>
-  <si>
-    <t>AIBL-2026-804183</t>
-  </si>
-  <si>
-    <t>AIBL-2026-358512</t>
-  </si>
-  <si>
-    <t>AIBL-2026-892681</t>
-  </si>
-  <si>
-    <t>AIBL-2026-545505</t>
-  </si>
-  <si>
-    <t>AIBL-2026-881986</t>
-  </si>
-  <si>
-    <t>AIBL-2026-473953</t>
-  </si>
-  <si>
-    <t>AIBL-2026-120623</t>
-  </si>
-  <si>
-    <t>AIBL-2026-173622</t>
-  </si>
-  <si>
-    <t>AIBL-2026-821573</t>
-  </si>
-  <si>
-    <t>AIBL-2026-404298</t>
-  </si>
-  <si>
-    <t>AIBL-2026-348879</t>
-  </si>
-  <si>
-    <t>AIBL-2026-148447</t>
-  </si>
-  <si>
-    <t>AIBL-2026-818459</t>
-  </si>
-  <si>
-    <t>AIBL-2026-976776</t>
-  </si>
-  <si>
-    <t>AIBL-2026-475148</t>
-  </si>
-  <si>
-    <t>AIBL-2026-805779</t>
-  </si>
-  <si>
-    <t>AIBL-2026-776689</t>
-  </si>
-  <si>
-    <t>AIBL-2026-690630</t>
-  </si>
-  <si>
-    <t>AIBL-2026-739320</t>
-  </si>
-  <si>
-    <t>AIBL-2026-567249</t>
-  </si>
-  <si>
-    <t>AIBL-2026-922069</t>
-  </si>
-  <si>
-    <t>AIBL-2026-716360</t>
-  </si>
-  <si>
-    <t>AIBL-2026-853700</t>
-  </si>
-  <si>
-    <t>AIBL-2026-565499</t>
-  </si>
-  <si>
-    <t>AIBL-2026-636337</t>
-  </si>
-  <si>
-    <t>AIBL-2026-959170</t>
-  </si>
-  <si>
-    <t>AIBL-2026-542836</t>
-  </si>
-  <si>
-    <t>AIBL-2026-779276</t>
-  </si>
-  <si>
-    <t>AIBL-2026-232562</t>
-  </si>
-  <si>
-    <t>AIBL-2026-743014</t>
-  </si>
-  <si>
-    <t>AIBL-2026-329563</t>
-  </si>
-  <si>
-    <t>AIBL-2026-631753</t>
-  </si>
-  <si>
-    <t>AIBL-2026-187842</t>
-  </si>
-  <si>
-    <t>AIBL-2026-143440</t>
-  </si>
-  <si>
-    <t>AIBL-2026-443297</t>
-  </si>
-  <si>
-    <t>AIBL-2026-165813</t>
-  </si>
-  <si>
-    <t>AIBL-2026-602688</t>
-  </si>
-  <si>
-    <t>AIBL-2026-892507</t>
-  </si>
-  <si>
-    <t>AIBL-2026-914941</t>
-  </si>
-  <si>
-    <t>AIBL-2026-513779</t>
-  </si>
-  <si>
-    <t>AIBL-2026-155473</t>
-  </si>
-  <si>
-    <t>AIBL-2026-748077</t>
-  </si>
-  <si>
-    <t>AIBL-2026-698760</t>
-  </si>
-  <si>
-    <t>AIBL-2026-432877</t>
-  </si>
-  <si>
-    <t>AIBL-2026-407979</t>
-  </si>
-  <si>
-    <t>AIBL-2026-268024</t>
-  </si>
-  <si>
-    <t>AIBL-2026-322069</t>
-  </si>
-  <si>
-    <t>AIBL-2026-468112</t>
-  </si>
-  <si>
-    <t>AIBL-2026-487619</t>
-  </si>
-  <si>
-    <t>AIBL-2026-257310</t>
-  </si>
-  <si>
-    <t>AIBL-2026-409200</t>
-  </si>
-  <si>
-    <t>AIBL-2026-794939</t>
-  </si>
-  <si>
-    <t>AIBL-2026-632010</t>
-  </si>
-  <si>
-    <t>AIBL-2026-845889</t>
-  </si>
-  <si>
-    <t>AIBL-2026-448119</t>
-  </si>
-  <si>
-    <t>AIBL-2026-281311</t>
-  </si>
-  <si>
-    <t>AIBL-2026-931001</t>
-  </si>
-  <si>
-    <t>AIBL-2026-799709</t>
-  </si>
-  <si>
-    <t>AIBL-2026-434431</t>
-  </si>
-  <si>
-    <t>AIBL-2026-952394</t>
-  </si>
-  <si>
-    <t>AIBL-2026-810943</t>
-  </si>
-  <si>
-    <t>AIBL-2026-615094</t>
-  </si>
-  <si>
-    <t>AIBL-2026-170832</t>
-  </si>
-  <si>
-    <t>AIBL-2026-790382</t>
-  </si>
-  <si>
-    <t>AIBL-2026-415806</t>
-  </si>
-  <si>
-    <t>AIBL-2026-350619</t>
-  </si>
-  <si>
-    <t>AIBL-2026-567636</t>
+    <t>AIBL-2026-609322</t>
+  </si>
+  <si>
+    <t>AIBL-2026-627124</t>
+  </si>
+  <si>
+    <t>AIBL-2026-187752</t>
+  </si>
+  <si>
+    <t>AIBL-2026-744827</t>
+  </si>
+  <si>
+    <t>AIBL-2026-146163</t>
+  </si>
+  <si>
+    <t>AIBL-2026-837116</t>
+  </si>
+  <si>
+    <t>AIBL-2026-883103</t>
+  </si>
+  <si>
+    <t>AIBL-2026-284019</t>
+  </si>
+  <si>
+    <t>AIBL-2026-336720</t>
+  </si>
+  <si>
+    <t>AIBL-2026-490628</t>
+  </si>
+  <si>
+    <t>AIBL-2026-645417</t>
   </si>
   <si>
     <t>AIBL-2026-117663</t>
   </si>
   <si>
+    <t>AIBL-2026-589814</t>
+  </si>
+  <si>
+    <t>AIBL-2026-212762</t>
+  </si>
+  <si>
     <t>AIBL-2026-912876</t>
   </si>
   <si>
     <t>AIBL-2026-754327</t>
   </si>
   <si>
+    <t>AIBL-2026-384298</t>
+  </si>
+  <si>
     <t>AIBL-2026-159071</t>
+  </si>
+  <si>
+    <t>AIBL-2026-326692</t>
+  </si>
+  <si>
+    <t>AIBL-2026-475972</t>
   </si>
   <si>
     <t>Source System</t>
@@ -1155,10 +1155,10 @@
         <v>46266</v>
       </c>
       <c r="E2" s="1">
-        <v>46269</v>
+        <v>46272</v>
       </c>
       <c r="F2" s="2">
-        <v>2.5</v>
+        <v>6.4</v>
       </c>
       <c r="G2" t="s">
         <v>11</v>
@@ -1181,10 +1181,10 @@
         <v>46266</v>
       </c>
       <c r="E3" s="1">
-        <v>46269</v>
+        <v>46270</v>
       </c>
       <c r="F3" s="2">
-        <v>2.7</v>
+        <v>3.8</v>
       </c>
       <c r="G3" t="s">
         <v>11</v>
@@ -1198,45 +1198,45 @@
         <v>17</v>
       </c>
       <c r="B4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" t="s">
         <v>18</v>
-      </c>
-      <c r="C4" t="s">
-        <v>19</v>
       </c>
       <c r="D4" s="1">
         <v>46266</v>
       </c>
       <c r="E4" s="1">
-        <v>46278</v>
+        <v>46271</v>
       </c>
       <c r="F4" s="2">
-        <v>11.6</v>
+        <v>5.4</v>
       </c>
       <c r="G4" t="s">
         <v>11</v>
       </c>
       <c r="H4" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C5" t="s">
         <v>21</v>
-      </c>
-      <c r="B5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C5" t="s">
-        <v>22</v>
       </c>
       <c r="D5" s="1">
         <v>46266</v>
       </c>
       <c r="E5" s="1">
-        <v>46274</v>
+        <v>46270</v>
       </c>
       <c r="F5" s="2">
-        <v>8.2</v>
+        <v>3.6</v>
       </c>
       <c r="G5" t="s">
         <v>11</v>
@@ -1247,169 +1247,169 @@
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D6" s="1">
+        <v>46267</v>
+      </c>
+      <c r="E6" s="1">
+        <v>46273</v>
+      </c>
+      <c r="F6" s="2">
+        <v>5.5</v>
+      </c>
+      <c r="G6" t="s">
+        <v>11</v>
+      </c>
+      <c r="H6" t="s">
         <v>23</v>
-      </c>
-      <c r="B6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C6" t="s">
-        <v>25</v>
-      </c>
-      <c r="D6" s="1">
-        <v>46266</v>
-      </c>
-      <c r="E6" s="1">
-        <v>46268</v>
-      </c>
-      <c r="F6" s="2">
-        <v>1.7</v>
-      </c>
-      <c r="G6" t="s">
-        <v>11</v>
-      </c>
-      <c r="H6" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" t="s">
+        <v>25</v>
+      </c>
+      <c r="D7" s="1">
+        <v>46267</v>
+      </c>
+      <c r="E7" s="1">
+        <v>46272</v>
+      </c>
+      <c r="F7" s="2">
+        <v>4.7</v>
+      </c>
+      <c r="G7" t="s">
+        <v>11</v>
+      </c>
+      <c r="H7" t="s">
         <v>26</v>
-      </c>
-      <c r="B7" t="s">
-        <v>24</v>
-      </c>
-      <c r="C7" t="s">
-        <v>27</v>
-      </c>
-      <c r="D7" s="1">
-        <v>46266</v>
-      </c>
-      <c r="E7" s="1">
-        <v>46268</v>
-      </c>
-      <c r="F7" s="2">
-        <v>2.1</v>
-      </c>
-      <c r="G7" t="s">
-        <v>11</v>
-      </c>
-      <c r="H7" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B8" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="C8" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="D8" s="1">
         <v>46267</v>
       </c>
       <c r="E8" s="1">
-        <v>46271</v>
+        <v>46270</v>
       </c>
       <c r="F8" s="2">
-        <v>4</v>
+        <v>2.5</v>
       </c>
       <c r="G8" t="s">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="H8" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="B9" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="C9" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D9" s="1">
         <v>46267</v>
       </c>
       <c r="E9" s="1">
-        <v>46272</v>
+        <v>46269</v>
       </c>
       <c r="F9" s="2">
-        <v>4.6</v>
+        <v>2.2</v>
       </c>
       <c r="G9" t="s">
         <v>11</v>
       </c>
       <c r="H9" t="s">
-        <v>16</v>
+        <v>32</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
+        <v>33</v>
+      </c>
+      <c r="B10" t="s">
+        <v>20</v>
+      </c>
+      <c r="C10" t="s">
         <v>34</v>
-      </c>
-      <c r="B10" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" t="s">
-        <v>30</v>
       </c>
       <c r="D10" s="1">
         <v>46267</v>
       </c>
       <c r="E10" s="1">
-        <v>46273</v>
+        <v>46272</v>
       </c>
       <c r="F10" s="2">
-        <v>6.1</v>
+        <v>4.8</v>
       </c>
       <c r="G10" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="H10" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
+        <v>35</v>
+      </c>
+      <c r="B11" t="s">
+        <v>20</v>
+      </c>
+      <c r="C11" t="s">
         <v>36</v>
-      </c>
-      <c r="B11" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11" t="s">
-        <v>10</v>
       </c>
       <c r="D11" s="1">
         <v>46267</v>
       </c>
       <c r="E11" s="1">
-        <v>46269</v>
+        <v>46270</v>
       </c>
       <c r="F11" s="2">
-        <v>2.4</v>
+        <v>2.8</v>
       </c>
       <c r="G11" t="s">
-        <v>37</v>
+        <v>11</v>
       </c>
       <c r="H11" t="s">
-        <v>28</v>
+        <v>12</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B12" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="C12" t="s">
-        <v>39</v>
+        <v>21</v>
       </c>
       <c r="D12" s="1">
         <v>46267</v>
@@ -1418,128 +1418,128 @@
         <v>46270</v>
       </c>
       <c r="F12" s="2">
-        <v>3.1</v>
+        <v>2.5</v>
       </c>
       <c r="G12" t="s">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="H12" t="s">
-        <v>31</v>
+        <v>16</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B13" t="s">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="C13" t="s">
-        <v>41</v>
+        <v>10</v>
       </c>
       <c r="D13" s="1">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="E13" s="1">
         <v>46271</v>
       </c>
       <c r="F13" s="2">
-        <v>4.4</v>
+        <v>2.8</v>
       </c>
       <c r="G13" t="s">
-        <v>37</v>
+        <v>11</v>
       </c>
       <c r="H13" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B14" t="s">
         <v>9</v>
       </c>
       <c r="C14" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="D14" s="1">
         <v>46268</v>
       </c>
       <c r="E14" s="1">
-        <v>46272</v>
+        <v>46270</v>
       </c>
       <c r="F14" s="2">
-        <v>3.6</v>
+        <v>1.9</v>
       </c>
       <c r="G14" t="s">
         <v>11</v>
       </c>
       <c r="H14" t="s">
-        <v>31</v>
+        <v>12</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B15" t="s">
         <v>9</v>
       </c>
       <c r="C15" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="D15" s="1">
         <v>46268</v>
       </c>
       <c r="E15" s="1">
-        <v>46270</v>
+        <v>46273</v>
       </c>
       <c r="F15" s="2">
-        <v>1.8</v>
+        <v>5.1</v>
       </c>
       <c r="G15" t="s">
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="H15" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B16" t="s">
         <v>9</v>
       </c>
       <c r="C16" t="s">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="D16" s="1">
         <v>46268</v>
       </c>
       <c r="E16" s="1">
-        <v>46273</v>
+        <v>46271</v>
       </c>
       <c r="F16" s="2">
-        <v>4.8</v>
+        <v>2.7</v>
       </c>
       <c r="G16" t="s">
         <v>11</v>
       </c>
       <c r="H16" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B17" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="C17" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="D17" s="1">
         <v>46268</v>
@@ -1548,88 +1548,88 @@
         <v>46271</v>
       </c>
       <c r="F17" s="2">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="G17" t="s">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="H17" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="B18" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="C18" t="s">
-        <v>47</v>
+        <v>25</v>
       </c>
       <c r="D18" s="1">
         <v>46268</v>
       </c>
       <c r="E18" s="1">
-        <v>46272</v>
+        <v>46270</v>
       </c>
       <c r="F18" s="2">
-        <v>4.4</v>
+        <v>1.9</v>
       </c>
       <c r="G18" t="s">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="H18" t="s">
-        <v>31</v>
+        <v>12</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="B19" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="C19" t="s">
-        <v>41</v>
+        <v>18</v>
       </c>
       <c r="D19" s="1">
         <v>46268</v>
       </c>
       <c r="E19" s="1">
-        <v>46271</v>
+        <v>46270</v>
       </c>
       <c r="F19" s="2">
-        <v>3.1</v>
+        <v>1.9</v>
       </c>
       <c r="G19" t="s">
         <v>11</v>
       </c>
       <c r="H19" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="B20" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="C20" t="s">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="D20" s="1">
         <v>46268</v>
       </c>
       <c r="E20" s="1">
-        <v>46271</v>
+        <v>46269</v>
       </c>
       <c r="F20" s="2">
-        <v>3.1</v>
+        <v>1.2</v>
       </c>
       <c r="G20" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="H20" t="s">
         <v>12</v>
@@ -1637,74 +1637,74 @@
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="B21" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="C21" t="s">
-        <v>41</v>
+        <v>21</v>
       </c>
       <c r="D21" s="1">
         <v>46268</v>
       </c>
       <c r="E21" s="1">
-        <v>46273</v>
+        <v>46270</v>
       </c>
       <c r="F21" s="2">
-        <v>4.7</v>
+        <v>2.2</v>
       </c>
       <c r="G21" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="H21" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="B22" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="C22" t="s">
-        <v>27</v>
+        <v>48</v>
       </c>
       <c r="D22" s="1">
         <v>46268</v>
       </c>
       <c r="E22" s="1">
-        <v>46273</v>
+        <v>46272</v>
       </c>
       <c r="F22" s="2">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="G22" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="H22" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="B23" t="s">
         <v>9</v>
       </c>
       <c r="C23" t="s">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="D23" s="1">
         <v>46269</v>
       </c>
       <c r="E23" s="1">
-        <v>46274</v>
+        <v>46273</v>
       </c>
       <c r="F23" s="2">
-        <v>4.9</v>
+        <v>4</v>
       </c>
       <c r="G23" t="s">
         <v>11</v>
@@ -1715,48 +1715,48 @@
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B24" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="C24" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="D24" s="1">
         <v>46269</v>
       </c>
       <c r="E24" s="1">
-        <v>46272</v>
+        <v>46270</v>
       </c>
       <c r="F24" s="2">
-        <v>3.2</v>
+        <v>1.2</v>
       </c>
       <c r="G24" t="s">
         <v>11</v>
       </c>
       <c r="H24" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B25" t="s">
         <v>9</v>
       </c>
       <c r="C25" t="s">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="D25" s="1">
-        <v>46269</v>
+        <v>46272</v>
       </c>
       <c r="E25" s="1">
-        <v>46271</v>
+        <v>46278</v>
       </c>
       <c r="F25" s="2">
-        <v>2.3</v>
+        <v>6.4</v>
       </c>
       <c r="G25" t="s">
         <v>11</v>
@@ -1767,129 +1767,129 @@
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B26" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="C26" t="s">
-        <v>56</v>
+        <v>10</v>
       </c>
       <c r="D26" s="1">
-        <v>46269</v>
+        <v>46272</v>
       </c>
       <c r="E26" s="1">
-        <v>46271</v>
+        <v>46274</v>
       </c>
       <c r="F26" s="2">
-        <v>1.6</v>
+        <v>2.1</v>
       </c>
       <c r="G26" t="s">
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="H26" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="B27" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="C27" t="s">
-        <v>56</v>
+        <v>25</v>
       </c>
       <c r="D27" s="1">
-        <v>46269</v>
+        <v>46272</v>
       </c>
       <c r="E27" s="1">
-        <v>46270</v>
+        <v>46276</v>
       </c>
       <c r="F27" s="2">
-        <v>1</v>
+        <v>4.2</v>
       </c>
       <c r="G27" t="s">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="H27" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="B28" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="C28" t="s">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="D28" s="1">
-        <v>46269</v>
+        <v>46272</v>
       </c>
       <c r="E28" s="1">
-        <v>46273</v>
+        <v>46275</v>
       </c>
       <c r="F28" s="2">
-        <v>4</v>
+        <v>2.7</v>
       </c>
       <c r="G28" t="s">
         <v>11</v>
       </c>
       <c r="H28" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="B29" t="s">
         <v>14</v>
       </c>
       <c r="C29" t="s">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="D29" s="1">
-        <v>46269</v>
+        <v>46272</v>
       </c>
       <c r="E29" s="1">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="F29" s="2">
-        <v>3.5</v>
+        <v>1.7</v>
       </c>
       <c r="G29" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="H29" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="B30" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="C30" t="s">
-        <v>10</v>
+        <v>58</v>
       </c>
       <c r="D30" s="1">
         <v>46272</v>
       </c>
       <c r="E30" s="1">
-        <v>46277</v>
+        <v>46275</v>
       </c>
       <c r="F30" s="2">
-        <v>5.3</v>
+        <v>3.4</v>
       </c>
       <c r="G30" t="s">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="H30" t="s">
         <v>16</v>
@@ -1897,51 +1897,51 @@
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B31" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="C31" t="s">
-        <v>30</v>
+        <v>58</v>
       </c>
       <c r="D31" s="1">
         <v>46272</v>
       </c>
       <c r="E31" s="1">
-        <v>46277</v>
+        <v>46275</v>
       </c>
       <c r="F31" s="2">
-        <v>5.4</v>
+        <v>2.9</v>
       </c>
       <c r="G31" t="s">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="H31" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B32" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="C32" t="s">
-        <v>33</v>
+        <v>58</v>
       </c>
       <c r="D32" s="1">
         <v>46272</v>
       </c>
       <c r="E32" s="1">
-        <v>46276</v>
+        <v>46273</v>
       </c>
       <c r="F32" s="2">
-        <v>3.5</v>
+        <v>1</v>
       </c>
       <c r="G32" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="H32" t="s">
         <v>12</v>
@@ -1949,13 +1949,13 @@
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B33" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="C33" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="D33" s="1">
         <v>46272</v>
@@ -1964,122 +1964,122 @@
         <v>46275</v>
       </c>
       <c r="F33" s="2">
-        <v>2.9</v>
+        <v>2.5</v>
       </c>
       <c r="G33" t="s">
         <v>11</v>
       </c>
       <c r="H33" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B34" t="s">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="C34" t="s">
-        <v>15</v>
+        <v>63</v>
       </c>
       <c r="D34" s="1">
         <v>46272</v>
       </c>
       <c r="E34" s="1">
-        <v>46274</v>
+        <v>46281</v>
       </c>
       <c r="F34" s="2">
-        <v>2.2</v>
+        <v>9.3</v>
       </c>
       <c r="G34" t="s">
         <v>11</v>
       </c>
       <c r="H34" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B35" t="s">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="C35" t="s">
-        <v>56</v>
+        <v>31</v>
       </c>
       <c r="D35" s="1">
         <v>46272</v>
       </c>
       <c r="E35" s="1">
-        <v>46276</v>
+        <v>46280</v>
       </c>
       <c r="F35" s="2">
-        <v>3.5</v>
+        <v>7.9</v>
       </c>
       <c r="G35" t="s">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="H35" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B36" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="C36" t="s">
-        <v>56</v>
+        <v>10</v>
       </c>
       <c r="D36" s="1">
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="E36" s="1">
-        <v>46276</v>
+        <v>46277</v>
       </c>
       <c r="F36" s="2">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="G36" t="s">
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="H36" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B37" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="C37" t="s">
-        <v>39</v>
+        <v>10</v>
       </c>
       <c r="D37" s="1">
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="E37" s="1">
-        <v>46274</v>
+        <v>46278</v>
       </c>
       <c r="F37" s="2">
-        <v>2.4</v>
+        <v>5.1</v>
       </c>
       <c r="G37" t="s">
         <v>11</v>
       </c>
       <c r="H37" t="s">
-        <v>31</v>
+        <v>12</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B38" t="s">
         <v>14</v>
@@ -2088,36 +2088,36 @@
         <v>15</v>
       </c>
       <c r="D38" s="1">
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="E38" s="1">
-        <v>46274</v>
+        <v>46276</v>
       </c>
       <c r="F38" s="2">
-        <v>2.1</v>
+        <v>2.6</v>
       </c>
       <c r="G38" t="s">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="H38" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B39" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="C39" t="s">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="D39" s="1">
-        <v>46272</v>
+        <v>46274</v>
       </c>
       <c r="E39" s="1">
-        <v>46274</v>
+        <v>46276</v>
       </c>
       <c r="F39" s="2">
         <v>2.3</v>
@@ -2126,111 +2126,111 @@
         <v>11</v>
       </c>
       <c r="H39" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B40" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="C40" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="D40" s="1">
-        <v>46272</v>
+        <v>46274</v>
       </c>
       <c r="E40" s="1">
-        <v>46273</v>
+        <v>46278</v>
       </c>
       <c r="F40" s="2">
-        <v>1.2</v>
+        <v>3.7</v>
       </c>
       <c r="G40" t="s">
         <v>11</v>
       </c>
       <c r="H40" t="s">
-        <v>16</v>
+        <v>32</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B41" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="C41" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="D41" s="1">
-        <v>46272</v>
+        <v>46274</v>
       </c>
       <c r="E41" s="1">
-        <v>46279</v>
+        <v>46278</v>
       </c>
       <c r="F41" s="2">
-        <v>7</v>
+        <v>3.5</v>
       </c>
       <c r="G41" t="s">
         <v>11</v>
       </c>
       <c r="H41" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B42" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="C42" t="s">
-        <v>19</v>
+        <v>58</v>
       </c>
       <c r="D42" s="1">
-        <v>46272</v>
+        <v>46274</v>
       </c>
       <c r="E42" s="1">
-        <v>46282</v>
+        <v>46277</v>
       </c>
       <c r="F42" s="2">
-        <v>9.6</v>
+        <v>3.4</v>
       </c>
       <c r="G42" t="s">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="H42" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
+        <v>72</v>
+      </c>
+      <c r="B43" t="s">
+        <v>30</v>
+      </c>
+      <c r="C43" t="s">
         <v>73</v>
       </c>
-      <c r="B43" t="s">
-        <v>24</v>
-      </c>
-      <c r="C43" t="s">
-        <v>41</v>
-      </c>
       <c r="D43" s="1">
-        <v>46272</v>
+        <v>46274</v>
       </c>
       <c r="E43" s="1">
-        <v>46274</v>
+        <v>46290</v>
       </c>
       <c r="F43" s="2">
-        <v>2.1</v>
+        <v>15.6</v>
       </c>
       <c r="G43" t="s">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="H43" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
@@ -2238,25 +2238,25 @@
         <v>74</v>
       </c>
       <c r="B44" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="C44" t="s">
-        <v>25</v>
+        <v>73</v>
       </c>
       <c r="D44" s="1">
-        <v>46272</v>
+        <v>46274</v>
       </c>
       <c r="E44" s="1">
-        <v>46275</v>
+        <v>46281</v>
       </c>
       <c r="F44" s="2">
-        <v>2.5</v>
+        <v>6.8</v>
       </c>
       <c r="G44" t="s">
         <v>11</v>
       </c>
       <c r="H44" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
@@ -2264,25 +2264,25 @@
         <v>75</v>
       </c>
       <c r="B45" t="s">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="C45" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="D45" s="1">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="E45" s="1">
-        <v>46275</v>
+        <v>46278</v>
       </c>
       <c r="F45" s="2">
-        <v>1.8</v>
+        <v>3.5</v>
       </c>
       <c r="G45" t="s">
         <v>11</v>
       </c>
       <c r="H45" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
@@ -2293,22 +2293,22 @@
         <v>9</v>
       </c>
       <c r="C46" t="s">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="D46" s="1">
-        <v>46273</v>
+        <v>46275</v>
       </c>
       <c r="E46" s="1">
         <v>46280</v>
       </c>
       <c r="F46" s="2">
-        <v>6.6</v>
+        <v>5.3</v>
       </c>
       <c r="G46" t="s">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="H46" t="s">
-        <v>31</v>
+        <v>12</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
@@ -2316,25 +2316,25 @@
         <v>77</v>
       </c>
       <c r="B47" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="C47" t="s">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="D47" s="1">
-        <v>46273</v>
+        <v>46275</v>
       </c>
       <c r="E47" s="1">
-        <v>46274</v>
+        <v>46277</v>
       </c>
       <c r="F47" s="2">
-        <v>1.4</v>
+        <v>1.9</v>
       </c>
       <c r="G47" t="s">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="H47" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
@@ -2342,25 +2342,25 @@
         <v>78</v>
       </c>
       <c r="B48" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="C48" t="s">
-        <v>39</v>
+        <v>10</v>
       </c>
       <c r="D48" s="1">
-        <v>46273</v>
+        <v>46275</v>
       </c>
       <c r="E48" s="1">
-        <v>46275</v>
+        <v>46281</v>
       </c>
       <c r="F48" s="2">
-        <v>1.9</v>
+        <v>5.7</v>
       </c>
       <c r="G48" t="s">
         <v>11</v>
       </c>
       <c r="H48" t="s">
-        <v>31</v>
+        <v>12</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
@@ -2368,25 +2368,25 @@
         <v>79</v>
       </c>
       <c r="B49" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="C49" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="D49" s="1">
-        <v>46273</v>
+        <v>46275</v>
       </c>
       <c r="E49" s="1">
         <v>46281</v>
       </c>
       <c r="F49" s="2">
-        <v>8.1</v>
+        <v>6.3</v>
       </c>
       <c r="G49" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="H49" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
@@ -2397,22 +2397,22 @@
         <v>9</v>
       </c>
       <c r="C50" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="D50" s="1">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="E50" s="1">
         <v>46277</v>
       </c>
       <c r="F50" s="2">
-        <v>2.8</v>
+        <v>1.7</v>
       </c>
       <c r="G50" t="s">
         <v>11</v>
       </c>
       <c r="H50" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.25">
@@ -2423,22 +2423,22 @@
         <v>9</v>
       </c>
       <c r="C51" t="s">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="D51" s="1">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="E51" s="1">
         <v>46277</v>
       </c>
       <c r="F51" s="2">
-        <v>2.7</v>
+        <v>1.9</v>
       </c>
       <c r="G51" t="s">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="H51" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.25">
@@ -2449,22 +2449,22 @@
         <v>14</v>
       </c>
       <c r="C52" t="s">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="D52" s="1">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="E52" s="1">
-        <v>46275</v>
+        <v>46277</v>
       </c>
       <c r="F52" s="2">
-        <v>1.4</v>
+        <v>2.2</v>
       </c>
       <c r="G52" t="s">
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="H52" t="s">
-        <v>12</v>
+        <v>32</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.25">
@@ -2472,25 +2472,25 @@
         <v>83</v>
       </c>
       <c r="B53" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="C53" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="D53" s="1">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="E53" s="1">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="F53" s="2">
-        <v>1.8</v>
+        <v>4.1</v>
       </c>
       <c r="G53" t="s">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="H53" t="s">
-        <v>31</v>
+        <v>16</v>
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.25">
@@ -2498,25 +2498,25 @@
         <v>84</v>
       </c>
       <c r="B54" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="C54" t="s">
-        <v>27</v>
+        <v>48</v>
       </c>
       <c r="D54" s="1">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="E54" s="1">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F54" s="2">
-        <v>4.6</v>
+        <v>5.1</v>
       </c>
       <c r="G54" t="s">
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="H54" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.25">
@@ -2524,19 +2524,19 @@
         <v>85</v>
       </c>
       <c r="B55" t="s">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="C55" t="s">
-        <v>27</v>
+        <v>50</v>
       </c>
       <c r="D55" s="1">
-        <v>46274</v>
+        <v>46276</v>
       </c>
       <c r="E55" s="1">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="F55" s="2">
-        <v>3.4</v>
+        <v>1.8</v>
       </c>
       <c r="G55" t="s">
         <v>11</v>
@@ -2550,25 +2550,25 @@
         <v>86</v>
       </c>
       <c r="B56" t="s">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="C56" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D56" s="1">
-        <v>46274</v>
+        <v>46276</v>
       </c>
       <c r="E56" s="1">
-        <v>46279</v>
+        <v>46278</v>
       </c>
       <c r="F56" s="2">
-        <v>5.1</v>
+        <v>1.6</v>
       </c>
       <c r="G56" t="s">
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="H56" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.25">
@@ -2579,22 +2579,22 @@
         <v>9</v>
       </c>
       <c r="C57" t="s">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="D57" s="1">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="E57" s="1">
-        <v>46280</v>
+        <v>46282</v>
       </c>
       <c r="F57" s="2">
-        <v>4.6</v>
+        <v>6.3</v>
       </c>
       <c r="G57" t="s">
         <v>11</v>
       </c>
       <c r="H57" t="s">
-        <v>31</v>
+        <v>12</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
@@ -2602,25 +2602,25 @@
         <v>88</v>
       </c>
       <c r="B58" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="C58" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D58" s="1">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="E58" s="1">
-        <v>46279</v>
+        <v>46277</v>
       </c>
       <c r="F58" s="2">
-        <v>3.6</v>
+        <v>0.9</v>
       </c>
       <c r="G58" t="s">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="H58" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.25">
@@ -2628,25 +2628,25 @@
         <v>89</v>
       </c>
       <c r="B59" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="C59" t="s">
-        <v>30</v>
+        <v>58</v>
       </c>
       <c r="D59" s="1">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="E59" s="1">
-        <v>46279</v>
+        <v>46278</v>
       </c>
       <c r="F59" s="2">
-        <v>4.2</v>
+        <v>2.3</v>
       </c>
       <c r="G59" t="s">
         <v>11</v>
       </c>
       <c r="H59" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.25">
@@ -2654,25 +2654,25 @@
         <v>90</v>
       </c>
       <c r="B60" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="C60" t="s">
-        <v>30</v>
+        <v>58</v>
       </c>
       <c r="D60" s="1">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="E60" s="1">
-        <v>46282</v>
+        <v>46278</v>
       </c>
       <c r="F60" s="2">
-        <v>6.7</v>
+        <v>1.7</v>
       </c>
       <c r="G60" t="s">
         <v>11</v>
       </c>
       <c r="H60" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.25">
@@ -2680,25 +2680,25 @@
         <v>91</v>
       </c>
       <c r="B61" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="C61" t="s">
-        <v>56</v>
+        <v>10</v>
       </c>
       <c r="D61" s="1">
-        <v>46275</v>
+        <v>46279</v>
       </c>
       <c r="E61" s="1">
-        <v>46278</v>
+        <v>46284</v>
       </c>
       <c r="F61" s="2">
-        <v>2.6</v>
+        <v>5.4</v>
       </c>
       <c r="G61" t="s">
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="H61" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.25">
@@ -2706,25 +2706,25 @@
         <v>92</v>
       </c>
       <c r="B62" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="C62" t="s">
-        <v>56</v>
+        <v>10</v>
       </c>
       <c r="D62" s="1">
-        <v>46275</v>
+        <v>46279</v>
       </c>
       <c r="E62" s="1">
-        <v>46276</v>
+        <v>46281</v>
       </c>
       <c r="F62" s="2">
-        <v>1.4</v>
+        <v>2.2</v>
       </c>
       <c r="G62" t="s">
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="H62" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.25">
@@ -2732,25 +2732,25 @@
         <v>93</v>
       </c>
       <c r="B63" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="C63" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="D63" s="1">
-        <v>46275</v>
+        <v>46279</v>
       </c>
       <c r="E63" s="1">
-        <v>46288</v>
+        <v>46285</v>
       </c>
       <c r="F63" s="2">
-        <v>12.7</v>
+        <v>6.3</v>
       </c>
       <c r="G63" t="s">
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="H63" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.25">
@@ -2758,25 +2758,25 @@
         <v>94</v>
       </c>
       <c r="B64" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="C64" t="s">
-        <v>47</v>
+        <v>10</v>
       </c>
       <c r="D64" s="1">
-        <v>46275</v>
+        <v>46279</v>
       </c>
       <c r="E64" s="1">
-        <v>46288</v>
+        <v>46286</v>
       </c>
       <c r="F64" s="2">
-        <v>12.6</v>
+        <v>6.5</v>
       </c>
       <c r="G64" t="s">
         <v>11</v>
       </c>
       <c r="H64" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.25">
@@ -2784,25 +2784,25 @@
         <v>95</v>
       </c>
       <c r="B65" t="s">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="C65" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="D65" s="1">
-        <v>46275</v>
+        <v>46279</v>
       </c>
       <c r="E65" s="1">
-        <v>46280</v>
+        <v>46285</v>
       </c>
       <c r="F65" s="2">
-        <v>5.1</v>
+        <v>6.4</v>
       </c>
       <c r="G65" t="s">
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="H65" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.25">
@@ -2810,25 +2810,25 @@
         <v>96</v>
       </c>
       <c r="B66" t="s">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="C66" t="s">
         <v>25</v>
       </c>
       <c r="D66" s="1">
-        <v>46275</v>
+        <v>46279</v>
       </c>
       <c r="E66" s="1">
-        <v>46277</v>
+        <v>46281</v>
       </c>
       <c r="F66" s="2">
-        <v>2.4</v>
+        <v>1.8</v>
       </c>
       <c r="G66" t="s">
         <v>11</v>
       </c>
       <c r="H66" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.25">
@@ -2836,56 +2836,56 @@
         <v>97</v>
       </c>
       <c r="B67" t="s">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="C67" t="s">
-        <v>98</v>
+        <v>25</v>
       </c>
       <c r="D67" s="1">
-        <v>46275</v>
+        <v>46279</v>
       </c>
       <c r="E67" s="1">
-        <v>46279</v>
+        <v>46284</v>
       </c>
       <c r="F67" s="2">
-        <v>4</v>
+        <v>4.7</v>
       </c>
       <c r="G67" t="s">
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="H67" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B68" t="s">
         <v>9</v>
       </c>
       <c r="C68" t="s">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="D68" s="1">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="E68" s="1">
-        <v>46281</v>
+        <v>46284</v>
       </c>
       <c r="F68" s="2">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="G68" t="s">
         <v>11</v>
       </c>
       <c r="H68" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B69" t="s">
         <v>9</v>
@@ -2894,264 +2894,264 @@
         <v>10</v>
       </c>
       <c r="D69" s="1">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="E69" s="1">
-        <v>46281</v>
+        <v>46285</v>
       </c>
       <c r="F69" s="2">
-        <v>4.8</v>
+        <v>6.4</v>
       </c>
       <c r="G69" t="s">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="H69" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B70" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="C70" t="s">
-        <v>30</v>
+        <v>58</v>
       </c>
       <c r="D70" s="1">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="E70" s="1">
-        <v>46279</v>
+        <v>46282</v>
       </c>
       <c r="F70" s="2">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="G70" t="s">
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="H70" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B71" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="C71" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="D71" s="1">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="E71" s="1">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F71" s="2">
-        <v>4.3</v>
+        <v>2.1</v>
       </c>
       <c r="G71" t="s">
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="H71" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B72" t="s">
         <v>14</v>
       </c>
       <c r="C72" t="s">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="D72" s="1">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="E72" s="1">
-        <v>46280</v>
+        <v>46283</v>
       </c>
       <c r="F72" s="2">
-        <v>4.1</v>
+        <v>3.6</v>
       </c>
       <c r="G72" t="s">
         <v>11</v>
       </c>
       <c r="H72" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B73" t="s">
         <v>14</v>
       </c>
       <c r="C73" t="s">
-        <v>39</v>
+        <v>18</v>
       </c>
       <c r="D73" s="1">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="E73" s="1">
-        <v>46278</v>
+        <v>46281</v>
       </c>
       <c r="F73" s="2">
-        <v>1.5</v>
+        <v>2.1</v>
       </c>
       <c r="G73" t="s">
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="H73" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B74" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="C74" t="s">
-        <v>41</v>
+        <v>18</v>
       </c>
       <c r="D74" s="1">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="E74" s="1">
-        <v>46278</v>
+        <v>46281</v>
       </c>
       <c r="F74" s="2">
-        <v>2.4</v>
+        <v>1.7</v>
       </c>
       <c r="G74" t="s">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="H74" t="s">
-        <v>31</v>
+        <v>12</v>
       </c>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B75" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="C75" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="D75" s="1">
         <v>46279</v>
       </c>
       <c r="E75" s="1">
-        <v>46284</v>
+        <v>46282</v>
       </c>
       <c r="F75" s="2">
-        <v>4.7</v>
+        <v>3.1</v>
       </c>
       <c r="G75" t="s">
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="H75" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B76" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="C76" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="D76" s="1">
         <v>46279</v>
       </c>
       <c r="E76" s="1">
-        <v>46282</v>
+        <v>46280</v>
       </c>
       <c r="F76" s="2">
-        <v>2.9</v>
+        <v>0.9</v>
       </c>
       <c r="G76" t="s">
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="H76" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B77" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="C77" t="s">
-        <v>33</v>
+        <v>58</v>
       </c>
       <c r="D77" s="1">
         <v>46279</v>
       </c>
       <c r="E77" s="1">
-        <v>46283</v>
+        <v>46281</v>
       </c>
       <c r="F77" s="2">
-        <v>4.4</v>
+        <v>1.9</v>
       </c>
       <c r="G77" t="s">
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="H77" t="s">
-        <v>31</v>
+        <v>12</v>
       </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B78" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="C78" t="s">
-        <v>10</v>
+        <v>58</v>
       </c>
       <c r="D78" s="1">
         <v>46279</v>
       </c>
       <c r="E78" s="1">
-        <v>46282</v>
+        <v>46281</v>
       </c>
       <c r="F78" s="2">
-        <v>3.1</v>
+        <v>2.2</v>
       </c>
       <c r="G78" t="s">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="H78" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
+        <v>109</v>
+      </c>
+      <c r="B79" t="s">
+        <v>30</v>
+      </c>
+      <c r="C79" t="s">
         <v>110</v>
-      </c>
-      <c r="B79" t="s">
-        <v>9</v>
-      </c>
-      <c r="C79" t="s">
-        <v>10</v>
       </c>
       <c r="D79" s="1">
         <v>46279</v>
@@ -3160,13 +3160,13 @@
         <v>46286</v>
       </c>
       <c r="F79" s="2">
-        <v>7.1</v>
+        <v>6.6</v>
       </c>
       <c r="G79" t="s">
         <v>11</v>
       </c>
       <c r="H79" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.25">
@@ -3174,25 +3174,25 @@
         <v>111</v>
       </c>
       <c r="B80" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="C80" t="s">
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="D80" s="1">
         <v>46279</v>
       </c>
       <c r="E80" s="1">
-        <v>46281</v>
+        <v>46292</v>
       </c>
       <c r="F80" s="2">
-        <v>1.8</v>
+        <v>13.4</v>
       </c>
       <c r="G80" t="s">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="H80" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.25">
@@ -3200,25 +3200,25 @@
         <v>112</v>
       </c>
       <c r="B81" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="C81" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="D81" s="1">
         <v>46279</v>
       </c>
       <c r="E81" s="1">
-        <v>46281</v>
+        <v>46284</v>
       </c>
       <c r="F81" s="2">
-        <v>2.4</v>
+        <v>4.7</v>
       </c>
       <c r="G81" t="s">
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="H81" t="s">
-        <v>28</v>
+        <v>12</v>
       </c>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.25">
@@ -3226,25 +3226,25 @@
         <v>113</v>
       </c>
       <c r="B82" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="C82" t="s">
-        <v>39</v>
+        <v>21</v>
       </c>
       <c r="D82" s="1">
         <v>46279</v>
       </c>
       <c r="E82" s="1">
-        <v>46282</v>
+        <v>46281</v>
       </c>
       <c r="F82" s="2">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="G82" t="s">
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="H82" t="s">
-        <v>31</v>
+        <v>12</v>
       </c>
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.25">
@@ -3252,25 +3252,25 @@
         <v>114</v>
       </c>
       <c r="B83" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="C83" t="s">
-        <v>39</v>
+        <v>21</v>
       </c>
       <c r="D83" s="1">
         <v>46279</v>
       </c>
       <c r="E83" s="1">
-        <v>46280</v>
+        <v>46283</v>
       </c>
       <c r="F83" s="2">
-        <v>1</v>
+        <v>4.4</v>
       </c>
       <c r="G83" t="s">
         <v>11</v>
       </c>
       <c r="H83" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.25">
@@ -3278,25 +3278,25 @@
         <v>115</v>
       </c>
       <c r="B84" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="C84" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="D84" s="1">
         <v>46279</v>
       </c>
       <c r="E84" s="1">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F84" s="2">
-        <v>2.3</v>
+        <v>2.7</v>
       </c>
       <c r="G84" t="s">
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="H84" t="s">
-        <v>16</v>
+        <v>32</v>
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.25">
@@ -3304,10 +3304,10 @@
         <v>116</v>
       </c>
       <c r="B85" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="C85" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="D85" s="1">
         <v>46279</v>
@@ -3316,13 +3316,13 @@
         <v>46282</v>
       </c>
       <c r="F85" s="2">
-        <v>3.1</v>
+        <v>2.5</v>
       </c>
       <c r="G85" t="s">
         <v>11</v>
       </c>
       <c r="H85" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.25">
@@ -3330,22 +3330,22 @@
         <v>117</v>
       </c>
       <c r="B86" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="C86" t="s">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="D86" s="1">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="E86" s="1">
-        <v>46281</v>
+        <v>46283</v>
       </c>
       <c r="F86" s="2">
-        <v>2.3</v>
+        <v>3.2</v>
       </c>
       <c r="G86" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="H86" t="s">
         <v>16</v>
@@ -3356,25 +3356,25 @@
         <v>118</v>
       </c>
       <c r="B87" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="C87" t="s">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="D87" s="1">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="E87" s="1">
-        <v>46282</v>
+        <v>46284</v>
       </c>
       <c r="F87" s="2">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="G87" t="s">
         <v>11</v>
       </c>
       <c r="H87" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.25">
@@ -3385,22 +3385,22 @@
         <v>14</v>
       </c>
       <c r="C88" t="s">
-        <v>39</v>
+        <v>18</v>
       </c>
       <c r="D88" s="1">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="E88" s="1">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F88" s="2">
         <v>2.9</v>
       </c>
       <c r="G88" t="s">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="H88" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.25">
@@ -3408,25 +3408,25 @@
         <v>120</v>
       </c>
       <c r="B89" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="C89" t="s">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="D89" s="1">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="E89" s="1">
-        <v>46292</v>
+        <v>46283</v>
       </c>
       <c r="F89" s="2">
-        <v>13</v>
+        <v>2.6</v>
       </c>
       <c r="G89" t="s">
         <v>11</v>
       </c>
       <c r="H89" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.25">
@@ -3434,25 +3434,25 @@
         <v>121</v>
       </c>
       <c r="B90" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="C90" t="s">
-        <v>41</v>
+        <v>73</v>
       </c>
       <c r="D90" s="1">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="E90" s="1">
-        <v>46284</v>
+        <v>46295</v>
       </c>
       <c r="F90" s="2">
-        <v>5.3</v>
+        <v>14.7</v>
       </c>
       <c r="G90" t="s">
         <v>11</v>
       </c>
       <c r="H90" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.25">
@@ -3460,25 +3460,25 @@
         <v>122</v>
       </c>
       <c r="B91" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="C91" t="s">
-        <v>27</v>
+        <v>73</v>
       </c>
       <c r="D91" s="1">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="E91" s="1">
-        <v>46283</v>
+        <v>46285</v>
       </c>
       <c r="F91" s="2">
-        <v>4.3</v>
+        <v>4.9</v>
       </c>
       <c r="G91" t="s">
         <v>11</v>
       </c>
       <c r="H91" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.25">
@@ -3486,19 +3486,19 @@
         <v>123</v>
       </c>
       <c r="B92" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="C92" t="s">
-        <v>98</v>
+        <v>110</v>
       </c>
       <c r="D92" s="1">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="E92" s="1">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F92" s="2">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="G92" t="s">
         <v>11</v>
@@ -3512,25 +3512,25 @@
         <v>124</v>
       </c>
       <c r="B93" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="C93" t="s">
-        <v>98</v>
+        <v>48</v>
       </c>
       <c r="D93" s="1">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="E93" s="1">
-        <v>46284</v>
+        <v>46283</v>
       </c>
       <c r="F93" s="2">
-        <v>5.2</v>
+        <v>2.9</v>
       </c>
       <c r="G93" t="s">
         <v>11</v>
       </c>
       <c r="H93" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.25">
@@ -3538,25 +3538,25 @@
         <v>125</v>
       </c>
       <c r="B94" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="C94" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="D94" s="1">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="E94" s="1">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F94" s="2">
-        <v>2.9</v>
+        <v>3.3</v>
       </c>
       <c r="G94" t="s">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="H94" t="s">
-        <v>12</v>
+        <v>32</v>
       </c>
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.25">
@@ -3564,25 +3564,25 @@
         <v>126</v>
       </c>
       <c r="B95" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="C95" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="D95" s="1">
         <v>46280</v>
       </c>
       <c r="E95" s="1">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F95" s="2">
-        <v>2.6</v>
+        <v>3.7</v>
       </c>
       <c r="G95" t="s">
         <v>11</v>
       </c>
       <c r="H95" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.25">
@@ -3590,25 +3590,25 @@
         <v>127</v>
       </c>
       <c r="B96" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="C96" t="s">
-        <v>56</v>
+        <v>25</v>
       </c>
       <c r="D96" s="1">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="E96" s="1">
-        <v>46283</v>
+        <v>46285</v>
       </c>
       <c r="F96" s="2">
-        <v>3.2</v>
+        <v>3.9</v>
       </c>
       <c r="G96" t="s">
         <v>11</v>
       </c>
       <c r="H96" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.25">
@@ -3616,48 +3616,48 @@
         <v>128</v>
       </c>
       <c r="B97" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="C97" t="s">
-        <v>129</v>
+        <v>25</v>
       </c>
       <c r="D97" s="1">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="E97" s="1">
-        <v>46293</v>
+        <v>46284</v>
       </c>
       <c r="F97" s="2">
-        <v>12.8</v>
+        <v>2.9</v>
       </c>
       <c r="G97" t="s">
         <v>11</v>
       </c>
       <c r="H97" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B98" t="s">
+        <v>14</v>
+      </c>
+      <c r="C98" t="s">
         <v>18</v>
       </c>
-      <c r="C98" t="s">
-        <v>47</v>
-      </c>
       <c r="D98" s="1">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="E98" s="1">
-        <v>46285</v>
+        <v>46283</v>
       </c>
       <c r="F98" s="2">
-        <v>4.9</v>
+        <v>1.9</v>
       </c>
       <c r="G98" t="s">
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="H98" t="s">
         <v>12</v>
@@ -3665,126 +3665,126 @@
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B99" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="C99" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="D99" s="1">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="E99" s="1">
-        <v>46288</v>
+        <v>46286</v>
       </c>
       <c r="F99" s="2">
-        <v>7.9</v>
+        <v>5</v>
       </c>
       <c r="G99" t="s">
         <v>11</v>
       </c>
       <c r="H99" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B100" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="C100" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="D100" s="1">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="E100" s="1">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F100" s="2">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="G100" t="s">
         <v>11</v>
       </c>
       <c r="H100" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B101" t="s">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="C101" t="s">
-        <v>98</v>
+        <v>25</v>
       </c>
       <c r="D101" s="1">
-        <v>46280</v>
+        <v>46282</v>
       </c>
       <c r="E101" s="1">
-        <v>46285</v>
+        <v>46288</v>
       </c>
       <c r="F101" s="2">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="G101" t="s">
         <v>11</v>
       </c>
       <c r="H101" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
     </row>
     <row r="102" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B102" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="C102" t="s">
-        <v>98</v>
+        <v>58</v>
       </c>
       <c r="D102" s="1">
-        <v>46280</v>
+        <v>46282</v>
       </c>
       <c r="E102" s="1">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F102" s="2">
-        <v>2.7</v>
+        <v>2.2</v>
       </c>
       <c r="G102" t="s">
         <v>11</v>
       </c>
       <c r="H102" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B103" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="C103" t="s">
-        <v>25</v>
+        <v>110</v>
       </c>
       <c r="D103" s="1">
-        <v>46280</v>
+        <v>46282</v>
       </c>
       <c r="E103" s="1">
-        <v>46285</v>
+        <v>46290</v>
       </c>
       <c r="F103" s="2">
-        <v>5.3</v>
+        <v>8.2</v>
       </c>
       <c r="G103" t="s">
         <v>11</v>
@@ -3795,48 +3795,48 @@
     </row>
     <row r="104" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B104" t="s">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="C104" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D104" s="1">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="E104" s="1">
-        <v>46286</v>
+        <v>46283</v>
       </c>
       <c r="F104" s="2">
-        <v>4.5</v>
+        <v>1.4</v>
       </c>
       <c r="G104" t="s">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="H104" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B105" t="s">
         <v>9</v>
       </c>
       <c r="C105" t="s">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="D105" s="1">
-        <v>46281</v>
+        <v>46283</v>
       </c>
       <c r="E105" s="1">
-        <v>46285</v>
+        <v>46289</v>
       </c>
       <c r="F105" s="2">
-        <v>3.7</v>
+        <v>5.5</v>
       </c>
       <c r="G105" t="s">
         <v>11</v>
@@ -3847,22 +3847,22 @@
     </row>
     <row r="106" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B106" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="C106" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="D106" s="1">
-        <v>46281</v>
+        <v>46283</v>
       </c>
       <c r="E106" s="1">
-        <v>46283</v>
+        <v>46285</v>
       </c>
       <c r="F106" s="2">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="G106" t="s">
         <v>11</v>
@@ -3873,279 +3873,279 @@
     </row>
     <row r="107" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B107" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="C107" t="s">
-        <v>22</v>
+        <v>110</v>
       </c>
       <c r="D107" s="1">
-        <v>46281</v>
+        <v>46283</v>
       </c>
       <c r="E107" s="1">
-        <v>46295</v>
+        <v>46291</v>
       </c>
       <c r="F107" s="2">
-        <v>13.7</v>
+        <v>8.4</v>
       </c>
       <c r="G107" t="s">
         <v>11</v>
       </c>
       <c r="H107" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="108" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B108" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="C108" t="s">
-        <v>27</v>
+        <v>73</v>
       </c>
       <c r="D108" s="1">
-        <v>46281</v>
+        <v>46283</v>
       </c>
       <c r="E108" s="1">
-        <v>46283</v>
+        <v>46296</v>
       </c>
       <c r="F108" s="2">
-        <v>1.9</v>
+        <v>13.2</v>
       </c>
       <c r="G108" t="s">
         <v>11</v>
       </c>
       <c r="H108" t="s">
-        <v>31</v>
+        <v>16</v>
       </c>
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B109" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="C109" t="s">
-        <v>30</v>
+        <v>63</v>
       </c>
       <c r="D109" s="1">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="E109" s="1">
-        <v>46289</v>
+        <v>46293</v>
       </c>
       <c r="F109" s="2">
-        <v>6.9</v>
+        <v>9.6</v>
       </c>
       <c r="G109" t="s">
         <v>11</v>
       </c>
       <c r="H109" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
     </row>
     <row r="110" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B110" t="s">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="C110" t="s">
-        <v>39</v>
+        <v>110</v>
       </c>
       <c r="D110" s="1">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="E110" s="1">
-        <v>46285</v>
+        <v>46290</v>
       </c>
       <c r="F110" s="2">
-        <v>2.9</v>
+        <v>6.9</v>
       </c>
       <c r="G110" t="s">
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="H110" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
     </row>
     <row r="111" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B111" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="C111" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="D111" s="1">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="E111" s="1">
-        <v>46284</v>
+        <v>46285</v>
       </c>
       <c r="F111" s="2">
-        <v>2.4</v>
+        <v>1.7</v>
       </c>
       <c r="G111" t="s">
         <v>11</v>
       </c>
       <c r="H111" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
     </row>
     <row r="112" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B112" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C112" t="s">
-        <v>47</v>
+        <v>21</v>
       </c>
       <c r="D112" s="1">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="E112" s="1">
-        <v>46288</v>
+        <v>46285</v>
       </c>
       <c r="F112" s="2">
-        <v>5.9</v>
+        <v>2.1</v>
       </c>
       <c r="G112" t="s">
         <v>11</v>
       </c>
       <c r="H112" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
     </row>
     <row r="113" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B113" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="C113" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="D113" s="1">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="E113" s="1">
-        <v>46285</v>
+        <v>46288</v>
       </c>
       <c r="F113" s="2">
-        <v>2.9</v>
+        <v>5.3</v>
       </c>
       <c r="G113" t="s">
         <v>11</v>
       </c>
       <c r="H113" t="s">
-        <v>31</v>
+        <v>16</v>
       </c>
     </row>
     <row r="114" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B114" t="s">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="C114" t="s">
-        <v>98</v>
+        <v>10</v>
       </c>
       <c r="D114" s="1">
-        <v>46282</v>
+        <v>46286</v>
       </c>
       <c r="E114" s="1">
-        <v>46285</v>
+        <v>46290</v>
       </c>
       <c r="F114" s="2">
-        <v>2.8</v>
+        <v>4</v>
       </c>
       <c r="G114" t="s">
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="H114" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
     </row>
     <row r="115" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B115" t="s">
         <v>9</v>
       </c>
       <c r="C115" t="s">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="D115" s="1">
-        <v>46283</v>
+        <v>46286</v>
       </c>
       <c r="E115" s="1">
         <v>46290</v>
       </c>
       <c r="F115" s="2">
-        <v>6.5</v>
+        <v>4.3</v>
       </c>
       <c r="G115" t="s">
         <v>11</v>
       </c>
       <c r="H115" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
     </row>
     <row r="116" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B116" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="C116" t="s">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="D116" s="1">
-        <v>46283</v>
+        <v>46286</v>
       </c>
       <c r="E116" s="1">
-        <v>46285</v>
+        <v>46291</v>
       </c>
       <c r="F116" s="2">
-        <v>2</v>
+        <v>5.1</v>
       </c>
       <c r="G116" t="s">
         <v>11</v>
       </c>
       <c r="H116" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="117" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B117" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="C117" t="s">
-        <v>39</v>
+        <v>10</v>
       </c>
       <c r="D117" s="1">
-        <v>46283</v>
+        <v>46286</v>
       </c>
       <c r="E117" s="1">
-        <v>46286</v>
+        <v>46289</v>
       </c>
       <c r="F117" s="2">
         <v>2.9</v>
@@ -4154,226 +4154,226 @@
         <v>11</v>
       </c>
       <c r="H117" t="s">
-        <v>28</v>
+        <v>12</v>
       </c>
     </row>
     <row r="118" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B118" t="s">
         <v>14</v>
       </c>
       <c r="C118" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D118" s="1">
-        <v>46283</v>
+        <v>46286</v>
       </c>
       <c r="E118" s="1">
-        <v>46286</v>
+        <v>46289</v>
       </c>
       <c r="F118" s="2">
         <v>3.3</v>
       </c>
       <c r="G118" t="s">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="H118" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
     </row>
     <row r="119" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B119" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="C119" t="s">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="D119" s="1">
-        <v>46283</v>
+        <v>46286</v>
       </c>
       <c r="E119" s="1">
-        <v>46297</v>
+        <v>46287</v>
       </c>
       <c r="F119" s="2">
-        <v>14.1</v>
+        <v>1.3</v>
       </c>
       <c r="G119" t="s">
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="H119" t="s">
-        <v>28</v>
+        <v>12</v>
       </c>
     </row>
     <row r="120" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B120" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="C120" t="s">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="D120" s="1">
-        <v>46283</v>
+        <v>46286</v>
       </c>
       <c r="E120" s="1">
-        <v>46287</v>
+        <v>46291</v>
       </c>
       <c r="F120" s="2">
-        <v>3.9</v>
+        <v>4.8</v>
       </c>
       <c r="G120" t="s">
         <v>11</v>
       </c>
       <c r="H120" t="s">
-        <v>31</v>
+        <v>16</v>
       </c>
     </row>
     <row r="121" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B121" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="C121" t="s">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="D121" s="1">
-        <v>46283</v>
+        <v>46286</v>
       </c>
       <c r="E121" s="1">
-        <v>46295</v>
+        <v>46288</v>
       </c>
       <c r="F121" s="2">
-        <v>12.4</v>
+        <v>2</v>
       </c>
       <c r="G121" t="s">
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="H121" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
     </row>
     <row r="122" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B122" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="C122" t="s">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="D122" s="1">
         <v>46286</v>
       </c>
       <c r="E122" s="1">
-        <v>46289</v>
+        <v>46287</v>
       </c>
       <c r="F122" s="2">
-        <v>2.5</v>
+        <v>1.1</v>
       </c>
       <c r="G122" t="s">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="H122" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="123" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B123" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="C123" t="s">
-        <v>30</v>
+        <v>58</v>
       </c>
       <c r="D123" s="1">
         <v>46286</v>
       </c>
       <c r="E123" s="1">
-        <v>46292</v>
+        <v>46290</v>
       </c>
       <c r="F123" s="2">
-        <v>5.8</v>
+        <v>3.7</v>
       </c>
       <c r="G123" t="s">
         <v>11</v>
       </c>
       <c r="H123" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
     </row>
     <row r="124" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B124" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="C124" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="D124" s="1">
         <v>46286</v>
       </c>
       <c r="E124" s="1">
-        <v>46289</v>
+        <v>46287</v>
       </c>
       <c r="F124" s="2">
-        <v>2.8</v>
+        <v>1.4</v>
       </c>
       <c r="G124" t="s">
         <v>11</v>
       </c>
       <c r="H124" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="125" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B125" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="C125" t="s">
-        <v>30</v>
+        <v>58</v>
       </c>
       <c r="D125" s="1">
         <v>46286</v>
       </c>
       <c r="E125" s="1">
-        <v>46291</v>
+        <v>46289</v>
       </c>
       <c r="F125" s="2">
-        <v>4.5</v>
+        <v>3.2</v>
       </c>
       <c r="G125" t="s">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="H125" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
     </row>
     <row r="126" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B126" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="C126" t="s">
-        <v>10</v>
+        <v>58</v>
       </c>
       <c r="D126" s="1">
         <v>46286</v>
@@ -4382,50 +4382,50 @@
         <v>46289</v>
       </c>
       <c r="F126" s="2">
-        <v>2.9</v>
+        <v>3.3</v>
       </c>
       <c r="G126" t="s">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="H126" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
     </row>
     <row r="127" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B127" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="C127" t="s">
-        <v>30</v>
+        <v>58</v>
       </c>
       <c r="D127" s="1">
         <v>46286</v>
       </c>
       <c r="E127" s="1">
-        <v>46291</v>
+        <v>46288</v>
       </c>
       <c r="F127" s="2">
-        <v>4.7</v>
+        <v>1.9</v>
       </c>
       <c r="G127" t="s">
         <v>11</v>
       </c>
       <c r="H127" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
     </row>
     <row r="128" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B128" t="s">
         <v>14</v>
       </c>
       <c r="C128" t="s">
-        <v>39</v>
+        <v>18</v>
       </c>
       <c r="D128" s="1">
         <v>46286</v>
@@ -4437,535 +4437,535 @@
         <v>1.6</v>
       </c>
       <c r="G128" t="s">
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="H128" t="s">
-        <v>12</v>
+        <v>32</v>
       </c>
     </row>
     <row r="129" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B129" t="s">
         <v>14</v>
       </c>
       <c r="C129" t="s">
-        <v>39</v>
+        <v>18</v>
       </c>
       <c r="D129" s="1">
         <v>46286</v>
       </c>
       <c r="E129" s="1">
-        <v>46289</v>
+        <v>46288</v>
       </c>
       <c r="F129" s="2">
-        <v>2.8</v>
+        <v>2.2</v>
       </c>
       <c r="G129" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="H129" t="s">
-        <v>31</v>
+        <v>12</v>
       </c>
     </row>
     <row r="130" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B130" t="s">
         <v>14</v>
       </c>
       <c r="C130" t="s">
-        <v>39</v>
+        <v>18</v>
       </c>
       <c r="D130" s="1">
         <v>46286</v>
       </c>
       <c r="E130" s="1">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="F130" s="2">
-        <v>1.1</v>
+        <v>2.4</v>
       </c>
       <c r="G130" t="s">
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="H130" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
     </row>
     <row r="131" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B131" t="s">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="C131" t="s">
-        <v>56</v>
+        <v>110</v>
       </c>
       <c r="D131" s="1">
         <v>46286</v>
       </c>
       <c r="E131" s="1">
-        <v>46288</v>
+        <v>46304</v>
       </c>
       <c r="F131" s="2">
-        <v>2.1</v>
+        <v>17.8</v>
       </c>
       <c r="G131" t="s">
         <v>11</v>
       </c>
       <c r="H131" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
     </row>
     <row r="132" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B132" t="s">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="C132" t="s">
-        <v>56</v>
+        <v>73</v>
       </c>
       <c r="D132" s="1">
         <v>46286</v>
       </c>
       <c r="E132" s="1">
-        <v>46289</v>
+        <v>46304</v>
       </c>
       <c r="F132" s="2">
-        <v>3.4</v>
+        <v>18.4</v>
       </c>
       <c r="G132" t="s">
         <v>11</v>
       </c>
       <c r="H132" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
     </row>
     <row r="133" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B133" t="s">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="C133" t="s">
-        <v>15</v>
+        <v>63</v>
       </c>
       <c r="D133" s="1">
         <v>46286</v>
       </c>
       <c r="E133" s="1">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F133" s="2">
-        <v>2.5</v>
+        <v>3.6</v>
       </c>
       <c r="G133" t="s">
         <v>11</v>
       </c>
       <c r="H133" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
     </row>
     <row r="134" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B134" t="s">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="C134" t="s">
-        <v>39</v>
+        <v>73</v>
       </c>
       <c r="D134" s="1">
         <v>46286</v>
       </c>
       <c r="E134" s="1">
-        <v>46287</v>
+        <v>46294</v>
       </c>
       <c r="F134" s="2">
-        <v>1.1</v>
+        <v>8</v>
       </c>
       <c r="G134" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="H134" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
     </row>
     <row r="135" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B135" t="s">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="C135" t="s">
-        <v>15</v>
+        <v>63</v>
       </c>
       <c r="D135" s="1">
         <v>46286</v>
       </c>
       <c r="E135" s="1">
-        <v>46289</v>
+        <v>46299</v>
       </c>
       <c r="F135" s="2">
-        <v>2.5</v>
+        <v>12.6</v>
       </c>
       <c r="G135" t="s">
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="H135" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
     <row r="136" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B136" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="C136" t="s">
-        <v>47</v>
+        <v>31</v>
       </c>
       <c r="D136" s="1">
         <v>46286</v>
       </c>
       <c r="E136" s="1">
-        <v>46290</v>
+        <v>46294</v>
       </c>
       <c r="F136" s="2">
-        <v>4</v>
+        <v>7.7</v>
       </c>
       <c r="G136" t="s">
         <v>11</v>
       </c>
       <c r="H136" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="137" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B137" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C137" t="s">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="D137" s="1">
         <v>46286</v>
       </c>
       <c r="E137" s="1">
-        <v>46298</v>
+        <v>46290</v>
       </c>
       <c r="F137" s="2">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="G137" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="H137" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="138" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B138" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C138" t="s">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="D138" s="1">
         <v>46286</v>
       </c>
       <c r="E138" s="1">
-        <v>46289</v>
+        <v>46291</v>
       </c>
       <c r="F138" s="2">
-        <v>3.1</v>
+        <v>4.6</v>
       </c>
       <c r="G138" t="s">
         <v>11</v>
       </c>
       <c r="H138" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="139" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B139" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C139" t="s">
-        <v>22</v>
+        <v>48</v>
       </c>
       <c r="D139" s="1">
         <v>46286</v>
       </c>
       <c r="E139" s="1">
-        <v>46296</v>
+        <v>46288</v>
       </c>
       <c r="F139" s="2">
-        <v>9.9</v>
+        <v>2.3</v>
       </c>
       <c r="G139" t="s">
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="H139" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
     </row>
     <row r="140" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B140" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="C140" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="D140" s="1">
         <v>46286</v>
       </c>
       <c r="E140" s="1">
-        <v>46289</v>
+        <v>46288</v>
       </c>
       <c r="F140" s="2">
-        <v>2.9</v>
+        <v>2.4</v>
       </c>
       <c r="G140" t="s">
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="H140" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
     </row>
     <row r="141" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B141" t="s">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="C141" t="s">
-        <v>27</v>
+        <v>50</v>
       </c>
       <c r="D141" s="1">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="E141" s="1">
-        <v>46288</v>
+        <v>46293</v>
       </c>
       <c r="F141" s="2">
-        <v>2.2</v>
+        <v>5.7</v>
       </c>
       <c r="G141" t="s">
         <v>11</v>
       </c>
       <c r="H141" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
     </row>
     <row r="142" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B142" t="s">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="C142" t="s">
-        <v>98</v>
+        <v>50</v>
       </c>
       <c r="D142" s="1">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="E142" s="1">
-        <v>46289</v>
+        <v>46291</v>
       </c>
       <c r="F142" s="2">
-        <v>3.3</v>
+        <v>4.1</v>
       </c>
       <c r="G142" t="s">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="H142" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="143" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B143" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="C143" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D143" s="1">
         <v>46287</v>
       </c>
       <c r="E143" s="1">
-        <v>46294</v>
+        <v>46289</v>
       </c>
       <c r="F143" s="2">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="G143" t="s">
         <v>11</v>
       </c>
       <c r="H143" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="144" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B144" t="s">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="C144" t="s">
-        <v>10</v>
+        <v>48</v>
       </c>
       <c r="D144" s="1">
         <v>46287</v>
       </c>
       <c r="E144" s="1">
-        <v>46290</v>
+        <v>46293</v>
       </c>
       <c r="F144" s="2">
-        <v>2.6</v>
+        <v>5.7</v>
       </c>
       <c r="G144" t="s">
         <v>11</v>
       </c>
       <c r="H144" t="s">
-        <v>31</v>
+        <v>12</v>
       </c>
     </row>
     <row r="145" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B145" t="s">
         <v>9</v>
       </c>
       <c r="C145" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="D145" s="1">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="E145" s="1">
-        <v>46293</v>
+        <v>46291</v>
       </c>
       <c r="F145" s="2">
-        <v>6.4</v>
+        <v>2.5</v>
       </c>
       <c r="G145" t="s">
         <v>11</v>
       </c>
       <c r="H145" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
     </row>
     <row r="146" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B146" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="C146" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D146" s="1">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="E146" s="1">
-        <v>46292</v>
+        <v>46290</v>
       </c>
       <c r="F146" s="2">
-        <v>4.7</v>
+        <v>2.4</v>
       </c>
       <c r="G146" t="s">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="H146" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
     </row>
     <row r="147" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B147" t="s">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="C147" t="s">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="D147" s="1">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="E147" s="1">
-        <v>46289</v>
+        <v>46293</v>
       </c>
       <c r="F147" s="2">
-        <v>2.4</v>
+        <v>4.9</v>
       </c>
       <c r="G147" t="s">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="H147" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="148" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B148" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="C148" t="s">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="D148" s="1">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="E148" s="1">
-        <v>46288</v>
+        <v>46292</v>
       </c>
       <c r="F148" s="2">
-        <v>1.3</v>
+        <v>3.7</v>
       </c>
       <c r="G148" t="s">
         <v>11</v>
       </c>
       <c r="H148" t="s">
-        <v>31</v>
+        <v>12</v>
       </c>
     </row>
     <row r="149" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B149" t="s">
         <v>14</v>
@@ -4974,102 +4974,102 @@
         <v>15</v>
       </c>
       <c r="D149" s="1">
-        <v>46287</v>
+        <v>46289</v>
       </c>
       <c r="E149" s="1">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F149" s="2">
-        <v>1.6</v>
+        <v>0.9</v>
       </c>
       <c r="G149" t="s">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="H149" t="s">
-        <v>16</v>
+        <v>32</v>
       </c>
     </row>
     <row r="150" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B150" t="s">
         <v>14</v>
       </c>
       <c r="C150" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D150" s="1">
-        <v>46287</v>
+        <v>46289</v>
       </c>
       <c r="E150" s="1">
-        <v>46289</v>
+        <v>46292</v>
       </c>
       <c r="F150" s="2">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
       <c r="G150" t="s">
         <v>11</v>
       </c>
       <c r="H150" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="151" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B151" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="C151" t="s">
-        <v>47</v>
+        <v>31</v>
       </c>
       <c r="D151" s="1">
-        <v>46287</v>
+        <v>46289</v>
       </c>
       <c r="E151" s="1">
-        <v>46298</v>
+        <v>46301</v>
       </c>
       <c r="F151" s="2">
-        <v>11.4</v>
+        <v>11.5</v>
       </c>
       <c r="G151" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="H151" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="152" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B152" t="s">
         <v>9</v>
       </c>
       <c r="C152" t="s">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="D152" s="1">
-        <v>46288</v>
+        <v>46290</v>
       </c>
       <c r="E152" s="1">
-        <v>46291</v>
+        <v>46296</v>
       </c>
       <c r="F152" s="2">
-        <v>3.3</v>
+        <v>5.6</v>
       </c>
       <c r="G152" t="s">
         <v>11</v>
       </c>
       <c r="H152" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
     </row>
     <row r="153" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B153" t="s">
         <v>9</v>
@@ -5078,279 +5078,279 @@
         <v>10</v>
       </c>
       <c r="D153" s="1">
-        <v>46288</v>
+        <v>46290</v>
       </c>
       <c r="E153" s="1">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F153" s="2">
-        <v>2.8</v>
+        <v>2</v>
       </c>
       <c r="G153" t="s">
         <v>11</v>
       </c>
       <c r="H153" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="154" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B154" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="C154" t="s">
-        <v>10</v>
+        <v>73</v>
       </c>
       <c r="D154" s="1">
-        <v>46288</v>
+        <v>46290</v>
       </c>
       <c r="E154" s="1">
-        <v>46290</v>
+        <v>46297</v>
       </c>
       <c r="F154" s="2">
-        <v>1.9</v>
+        <v>6.9</v>
       </c>
       <c r="G154" t="s">
         <v>11</v>
       </c>
       <c r="H154" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
     </row>
     <row r="155" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B155" t="s">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="C155" t="s">
-        <v>10</v>
+        <v>48</v>
       </c>
       <c r="D155" s="1">
-        <v>46288</v>
+        <v>46290</v>
       </c>
       <c r="E155" s="1">
-        <v>46294</v>
+        <v>46293</v>
       </c>
       <c r="F155" s="2">
-        <v>6.2</v>
+        <v>2.5</v>
       </c>
       <c r="G155" t="s">
         <v>11</v>
       </c>
       <c r="H155" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
     </row>
     <row r="156" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B156" t="s">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="C156" t="s">
-        <v>10</v>
+        <v>48</v>
       </c>
       <c r="D156" s="1">
-        <v>46288</v>
+        <v>46290</v>
       </c>
       <c r="E156" s="1">
         <v>46292</v>
       </c>
       <c r="F156" s="2">
-        <v>3.9</v>
+        <v>1.7</v>
       </c>
       <c r="G156" t="s">
         <v>11</v>
       </c>
       <c r="H156" t="s">
-        <v>31</v>
+        <v>16</v>
       </c>
     </row>
     <row r="157" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B157" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="C157" t="s">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="D157" s="1">
-        <v>46288</v>
+        <v>46293</v>
       </c>
       <c r="E157" s="1">
-        <v>46292</v>
+        <v>46295</v>
       </c>
       <c r="F157" s="2">
-        <v>3.5</v>
+        <v>1.8</v>
       </c>
       <c r="G157" t="s">
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="H157" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="158" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B158" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="C158" t="s">
-        <v>129</v>
+        <v>10</v>
       </c>
       <c r="D158" s="1">
-        <v>46288</v>
+        <v>46293</v>
       </c>
       <c r="E158" s="1">
-        <v>46294</v>
+        <v>46297</v>
       </c>
       <c r="F158" s="2">
-        <v>6.3</v>
+        <v>4.3</v>
       </c>
       <c r="G158" t="s">
         <v>11</v>
       </c>
       <c r="H158" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
     </row>
     <row r="159" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B159" t="s">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="C159" t="s">
-        <v>98</v>
+        <v>25</v>
       </c>
       <c r="D159" s="1">
-        <v>46288</v>
+        <v>46293</v>
       </c>
       <c r="E159" s="1">
-        <v>46291</v>
+        <v>46299</v>
       </c>
       <c r="F159" s="2">
-        <v>3</v>
+        <v>5.9</v>
       </c>
       <c r="G159" t="s">
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="H159" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
     </row>
     <row r="160" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B160" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="C160" t="s">
-        <v>47</v>
+        <v>10</v>
       </c>
       <c r="D160" s="1">
-        <v>46289</v>
+        <v>46293</v>
       </c>
       <c r="E160" s="1">
-        <v>46295</v>
+        <v>46298</v>
       </c>
       <c r="F160" s="2">
-        <v>6.4</v>
+        <v>4.7</v>
       </c>
       <c r="G160" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="H160" t="s">
-        <v>31</v>
+        <v>12</v>
       </c>
     </row>
     <row r="161" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B161" t="s">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="C161" t="s">
-        <v>27</v>
+        <v>50</v>
       </c>
       <c r="D161" s="1">
-        <v>46289</v>
+        <v>46293</v>
       </c>
       <c r="E161" s="1">
-        <v>46293</v>
+        <v>46296</v>
       </c>
       <c r="F161" s="2">
-        <v>3.9</v>
+        <v>3</v>
       </c>
       <c r="G161" t="s">
         <v>11</v>
       </c>
       <c r="H161" t="s">
-        <v>31</v>
+        <v>16</v>
       </c>
     </row>
     <row r="162" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B162" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="C162" t="s">
-        <v>39</v>
+        <v>25</v>
       </c>
       <c r="D162" s="1">
-        <v>46290</v>
+        <v>46293</v>
       </c>
       <c r="E162" s="1">
-        <v>46293</v>
+        <v>46298</v>
       </c>
       <c r="F162" s="2">
-        <v>2.5</v>
+        <v>5.4</v>
       </c>
       <c r="G162" t="s">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="H162" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="163" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
+        <v>194</v>
+      </c>
+      <c r="B163" t="s">
+        <v>9</v>
+      </c>
+      <c r="C163" t="s">
+        <v>25</v>
+      </c>
+      <c r="D163" s="1">
+        <v>46293</v>
+      </c>
+      <c r="E163" s="1">
+        <v>46298</v>
+      </c>
+      <c r="F163" s="2">
+        <v>5.4</v>
+      </c>
+      <c r="G163" t="s">
         <v>195</v>
       </c>
-      <c r="B163" t="s">
-        <v>24</v>
-      </c>
-      <c r="C163" t="s">
-        <v>27</v>
-      </c>
-      <c r="D163" s="1">
-        <v>46290</v>
-      </c>
-      <c r="E163" s="1">
-        <v>46292</v>
-      </c>
-      <c r="F163" s="2">
-        <v>2.2</v>
-      </c>
-      <c r="G163" t="s">
-        <v>11</v>
-      </c>
       <c r="H163" t="s">
-        <v>28</v>
+        <v>12</v>
       </c>
     </row>
     <row r="164" spans="1:8" x14ac:dyDescent="0.25">
@@ -5358,25 +5358,25 @@
         <v>196</v>
       </c>
       <c r="B164" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="C164" t="s">
-        <v>41</v>
+        <v>58</v>
       </c>
       <c r="D164" s="1">
-        <v>46290</v>
+        <v>46293</v>
       </c>
       <c r="E164" s="1">
-        <v>46293</v>
+        <v>46297</v>
       </c>
       <c r="F164" s="2">
-        <v>3.1</v>
+        <v>3.7</v>
       </c>
       <c r="G164" t="s">
         <v>11</v>
       </c>
       <c r="H164" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
     </row>
     <row r="165" spans="1:8" x14ac:dyDescent="0.25">
@@ -5384,25 +5384,25 @@
         <v>197</v>
       </c>
       <c r="B165" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="C165" t="s">
-        <v>10</v>
+        <v>58</v>
       </c>
       <c r="D165" s="1">
         <v>46293</v>
       </c>
       <c r="E165" s="1">
-        <v>46298</v>
+        <v>46295</v>
       </c>
       <c r="F165" s="2">
-        <v>4.9</v>
+        <v>2.4</v>
       </c>
       <c r="G165" t="s">
         <v>11</v>
       </c>
       <c r="H165" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
     </row>
     <row r="166" spans="1:8" x14ac:dyDescent="0.25">
@@ -5410,25 +5410,25 @@
         <v>198</v>
       </c>
       <c r="B166" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="C166" t="s">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="D166" s="1">
         <v>46293</v>
       </c>
       <c r="E166" s="1">
-        <v>46298</v>
+        <v>46295</v>
       </c>
       <c r="F166" s="2">
-        <v>4.9</v>
+        <v>1.8</v>
       </c>
       <c r="G166" t="s">
         <v>11</v>
       </c>
       <c r="H166" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="167" spans="1:8" x14ac:dyDescent="0.25">
@@ -5436,25 +5436,25 @@
         <v>199</v>
       </c>
       <c r="B167" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="C167" t="s">
-        <v>10</v>
+        <v>73</v>
       </c>
       <c r="D167" s="1">
         <v>46293</v>
       </c>
       <c r="E167" s="1">
-        <v>46296</v>
+        <v>46305</v>
       </c>
       <c r="F167" s="2">
-        <v>2.6</v>
+        <v>11.7</v>
       </c>
       <c r="G167" t="s">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="H167" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
     </row>
     <row r="168" spans="1:8" x14ac:dyDescent="0.25">
@@ -5462,25 +5462,25 @@
         <v>200</v>
       </c>
       <c r="B168" t="s">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="C168" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="D168" s="1">
         <v>46293</v>
       </c>
       <c r="E168" s="1">
-        <v>46299</v>
+        <v>46298</v>
       </c>
       <c r="F168" s="2">
-        <v>6.4</v>
+        <v>4.8</v>
       </c>
       <c r="G168" t="s">
-        <v>35</v>
+        <v>195</v>
       </c>
       <c r="H168" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="169" spans="1:8" x14ac:dyDescent="0.25">
@@ -5488,22 +5488,22 @@
         <v>201</v>
       </c>
       <c r="B169" t="s">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="C169" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D169" s="1">
         <v>46293</v>
       </c>
       <c r="E169" s="1">
-        <v>46299</v>
+        <v>46295</v>
       </c>
       <c r="F169" s="2">
-        <v>6.3</v>
+        <v>1.6</v>
       </c>
       <c r="G169" t="s">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="H169" t="s">
         <v>16</v>
@@ -5520,16 +5520,16 @@
         <v>10</v>
       </c>
       <c r="D170" s="1">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="E170" s="1">
-        <v>46300</v>
+        <v>46299</v>
       </c>
       <c r="F170" s="2">
-        <v>6.9</v>
+        <v>4.5</v>
       </c>
       <c r="G170" t="s">
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="H170" t="s">
         <v>16</v>
@@ -5540,25 +5540,25 @@
         <v>203</v>
       </c>
       <c r="B171" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="C171" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="D171" s="1">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="E171" s="1">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F171" s="2">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="G171" t="s">
         <v>11</v>
       </c>
       <c r="H171" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
     </row>
     <row r="172" spans="1:8" x14ac:dyDescent="0.25">
@@ -5569,22 +5569,22 @@
         <v>14</v>
       </c>
       <c r="C172" t="s">
-        <v>15</v>
+        <v>58</v>
       </c>
       <c r="D172" s="1">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="E172" s="1">
         <v>46296</v>
       </c>
       <c r="F172" s="2">
-        <v>3</v>
+        <v>1.6</v>
       </c>
       <c r="G172" t="s">
         <v>11</v>
       </c>
       <c r="H172" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="173" spans="1:8" x14ac:dyDescent="0.25">
@@ -5592,25 +5592,25 @@
         <v>205</v>
       </c>
       <c r="B173" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C173" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D173" s="1">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="E173" s="1">
-        <v>46302</v>
+        <v>46299</v>
       </c>
       <c r="F173" s="2">
-        <v>8.5</v>
+        <v>4.8</v>
       </c>
       <c r="G173" t="s">
         <v>11</v>
       </c>
       <c r="H173" t="s">
-        <v>31</v>
+        <v>16</v>
       </c>
     </row>
     <row r="174" spans="1:8" x14ac:dyDescent="0.25">
@@ -5618,25 +5618,25 @@
         <v>206</v>
       </c>
       <c r="B174" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C174" t="s">
-        <v>47</v>
+        <v>21</v>
       </c>
       <c r="D174" s="1">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="E174" s="1">
-        <v>46307</v>
+        <v>46298</v>
       </c>
       <c r="F174" s="2">
-        <v>14.1</v>
+        <v>4.4</v>
       </c>
       <c r="G174" t="s">
         <v>11</v>
       </c>
       <c r="H174" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
     <row r="175" spans="1:8" x14ac:dyDescent="0.25">
@@ -5644,25 +5644,25 @@
         <v>207</v>
       </c>
       <c r="B175" t="s">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="C175" t="s">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="D175" s="1">
-        <v>46293</v>
+        <v>46295</v>
       </c>
       <c r="E175" s="1">
-        <v>46295</v>
+        <v>46300</v>
       </c>
       <c r="F175" s="2">
-        <v>2.3</v>
+        <v>5.4</v>
       </c>
       <c r="G175" t="s">
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="H175" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
     </row>
     <row r="176" spans="1:8" x14ac:dyDescent="0.25">
@@ -5673,22 +5673,22 @@
         <v>9</v>
       </c>
       <c r="C176" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="D176" s="1">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="E176" s="1">
-        <v>46296</v>
+        <v>46299</v>
       </c>
       <c r="F176" s="2">
-        <v>2</v>
+        <v>3.5</v>
       </c>
       <c r="G176" t="s">
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="H176" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
     </row>
     <row r="177" spans="1:8" x14ac:dyDescent="0.25">
@@ -5699,22 +5699,22 @@
         <v>9</v>
       </c>
       <c r="C177" t="s">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="D177" s="1">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="E177" s="1">
-        <v>46296</v>
+        <v>46299</v>
       </c>
       <c r="F177" s="2">
-        <v>2.4</v>
+        <v>4</v>
       </c>
       <c r="G177" t="s">
         <v>11</v>
       </c>
       <c r="H177" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
     <row r="178" spans="1:8" x14ac:dyDescent="0.25">
@@ -5722,25 +5722,25 @@
         <v>210</v>
       </c>
       <c r="B178" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="C178" t="s">
-        <v>47</v>
+        <v>10</v>
       </c>
       <c r="D178" s="1">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="E178" s="1">
-        <v>46308</v>
+        <v>46302</v>
       </c>
       <c r="F178" s="2">
-        <v>13.7</v>
+        <v>6.5</v>
       </c>
       <c r="G178" t="s">
         <v>11</v>
       </c>
       <c r="H178" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
     </row>
     <row r="179" spans="1:8" x14ac:dyDescent="0.25">
@@ -5748,25 +5748,25 @@
         <v>211</v>
       </c>
       <c r="B179" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="C179" t="s">
-        <v>33</v>
+        <v>110</v>
       </c>
       <c r="D179" s="1">
         <v>46295</v>
       </c>
       <c r="E179" s="1">
-        <v>46297</v>
+        <v>46303</v>
       </c>
       <c r="F179" s="2">
-        <v>2.2</v>
+        <v>7.6</v>
       </c>
       <c r="G179" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="H179" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
     </row>
     <row r="180" spans="1:8" x14ac:dyDescent="0.25">
@@ -5774,25 +5774,25 @@
         <v>212</v>
       </c>
       <c r="B180" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="C180" t="s">
-        <v>10</v>
+        <v>63</v>
       </c>
       <c r="D180" s="1">
         <v>46295</v>
       </c>
       <c r="E180" s="1">
-        <v>46299</v>
+        <v>46303</v>
       </c>
       <c r="F180" s="2">
-        <v>4.4</v>
+        <v>7.8</v>
       </c>
       <c r="G180" t="s">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="H180" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
     </row>
     <row r="181" spans="1:8" x14ac:dyDescent="0.25">
@@ -5800,25 +5800,25 @@
         <v>213</v>
       </c>
       <c r="B181" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="C181" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D181" s="1">
         <v>46295</v>
       </c>
       <c r="E181" s="1">
-        <v>46300</v>
+        <v>46310</v>
       </c>
       <c r="F181" s="2">
-        <v>4.6</v>
+        <v>14.9</v>
       </c>
       <c r="G181" t="s">
         <v>11</v>
       </c>
       <c r="H181" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
     <row r="182" spans="1:8" x14ac:dyDescent="0.25">
@@ -5826,25 +5826,25 @@
         <v>214</v>
       </c>
       <c r="B182" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="C182" t="s">
-        <v>22</v>
+        <v>73</v>
       </c>
       <c r="D182" s="1">
         <v>46295</v>
       </c>
       <c r="E182" s="1">
-        <v>46302</v>
+        <v>46299</v>
       </c>
       <c r="F182" s="2">
-        <v>7.1</v>
+        <v>4.2</v>
       </c>
       <c r="G182" t="s">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="H182" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
     </row>
     <row r="183" spans="1:8" x14ac:dyDescent="0.25">
@@ -5852,25 +5852,25 @@
         <v>215</v>
       </c>
       <c r="B183" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C183" t="s">
-        <v>129</v>
+        <v>21</v>
       </c>
       <c r="D183" s="1">
         <v>46295</v>
       </c>
       <c r="E183" s="1">
-        <v>46303</v>
+        <v>46299</v>
       </c>
       <c r="F183" s="2">
-        <v>7.5</v>
+        <v>4</v>
       </c>
       <c r="G183" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="H183" t="s">
-        <v>12</v>
+        <v>32</v>
       </c>
     </row>
   </sheetData>
